--- a/data/export_data.xlsx
+++ b/data/export_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,335 +437,4910 @@
           <t>target_circle</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nhtnkhungmadthvcl/video/7399490740759334162</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7487584018771299590</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nhạc chất quá 😎 dokieng tiktok</t>
+          <t>Nyc có nym</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>#sirus #sirusdokieng #xedovietnam #racing #xuhuong #xuhuongtiktok</t>
+          <t>#alominhngheday #broadenmyhorizon #podcast #tinhyeu #nyc #tamsu #trending #fyp</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>xe độ chiến</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nhtnkhungmadthvcl/video/7405055532932861191</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7454497923116715272</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>_mê sĩ gút điểm danh 🥰 dokieng tiktok</t>
+          <t>Một năm với nhiều cảm xúc lẫn lộn, vui có buồn có, khóc thật nhiều cũng có. Năm 2024 khép lại, muốn cảm ơn bản thân thật nhiều vì đã cố gắng hết mình ❤️ Mong năm mới mọi điều mới, vạn điều may, chúc mọi người năm mới sức khoẻ, hạnh phúc và bình an🌸</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>#sirus #sirusdokieng #xedovietnam #racing #xuhuong #xuhuongtiktok #capcut</t>
+          <t>#alominhngheday #broadenmyhorizon #podcasts #2024 #chucmungnammoi #tamsu #xuhuong</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>xe độ chiến</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nhtnkhungmadthvcl/video/7406878844088634632</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7291131414848867585</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>_flop quá 🤕 dokieng tiktok</t>
+          <t>Một chút động lực cho mỗi chúng ta Nếu có thấy cuộc sống bế tắc quá, hãy nhớ về những "tấm lưng" nhọc nhằn của cha mẹ chưa từng biết mỏi Nếu thấy học hành vất vả quá, hãy nhớ mỗi một con chữ bạn đang nhận được đã phải trả giá bằng một giọt mồ hôi của cha mẹ Hãy nhớ bạn đang dùng số tiền mà bố mẹ cực khổ kiếm được để học những tri thức mà họ không hiểu được Vì vậy mà, cố lên mà học hành cho tốt, mà sống cho ra hồn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>#sirus #sirusdokieng #xedovietnam #xuhuong #xuhuongtiktok #capcut</t>
+          <t>#alominhngheday #broadenmyhorizon #motivation #dongluchoctap #healing #podcast #trending</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>xe độ chiến</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nhtnkhungmadthvcl/video/7407343296630099218</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7486001659408157970</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>món đồ đắt nhất trên xe bạn là?? dokieng tiktok</t>
+          <t>Bình yên rồi sẽ đến Ai trong chúng ta cũng xứng đáng có được bình yên 🪴</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>#sirus #sirusdokieng #xedovietnam #xuhuong #xuhuongtiktok #capcut</t>
+          <t>#alominhngheday #broadenmyhorizon #podcast #binhyen #nhansinhtutaimotkiepbinhan #healing #tamsu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>xe độ chiến</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nhtnkhungmadthvcl/video/7404663913662467346</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7453454003926519047</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>_tự tin ăn đứt 50cc 😋 tiktok</t>
+          <t>❤️Thời gian thích hợp gặp một người thích hợp là hạnh phúc 💔Thời gian thích hợp gặp một người không thích hợp là sai lầm 🖤Thời gian không thích hợp gặp một người không thích hợp là viển vông 💔Thời gian không thích hợp gặp một người thích hợp là tiếc nuối</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>#xediendo #xedovietnam #racing #xuhuong #xuhuongtiktok #capcut</t>
+          <t>#alominhngheday #broadenmyhorizon #podcasts #tinhyeu #tamsu #xuhuong</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>xe độ chiến</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nhtnkhungmadthvcl/video/7399099608615505160</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7452709627000589586</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>_mê si rút vào điểm danh 🥰 dokieng tiktok</t>
+          <t>Cậu từng trải quan cảm giác hiểu được sự quan trọng của một ai đó, nhưng là khi ... họ đã rời đi chưa?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>#sirus #sirusdokieng #xedovietnam #racing #xuhuong #xuhuongtiktok</t>
+          <t>#alominhngheday #broadenmyhorizon #love #tamsu #tinhyeu #podcasts #xuhuong</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>xe độ chiến</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nhtnkhungmadthvcl/video/7399258593712704786</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7454170010672581896</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>_nếu có 200 củ ae mua xe gì 🤔 dokieng tiktok</t>
+          <t>Ước làm một cái cây, bình yên giữa cuộc đời 🌱</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>#sirus #sirusdokieng #xedovietnam #racing #xuhuong #xuhuongtiktok</t>
+          <t>#alominhngheday #broadenmyhorizon #podcasts #tamsu #healing #xuhuong</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>xe độ chiến</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nhtnkhungmadthvcl/video/7404473283569077511</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7450346158150405384</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>_nhìn em nó nhỏ nhoi 🥰 dokieng tiktok</t>
+          <t>Khi lớn lên rồi, đâu ai nghĩ mấy đứa trẻ con từng chơi chung trong xóm lại hỏi nhau câu này " Tết này, về không mày?!"</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>#sirus #sirusdokieng #xedovietnam #racing #xuhuong #xuhuongtiktok #capcut</t>
+          <t>#alominhngheday #broadenmyhorizon #tet #giadinh #happynewyear #podcasts #tamsu #xuhuong</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>xe độ chiến</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nhtnkhungmadthvcl/video/7398922834547887367</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7480842982338366728</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>_mang tiếng xe kiểng 🥰 dokieng tiktok</t>
+          <t>Liệu chúng mình có đang thực sự "Sống" hay chỉ cố để "Tồn tại" 🌸</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>#sirus #sirusdokieng #xedovietnam #racing #xuhuong #xuhuongtiktok</t>
+          <t>#alominhngheday #broadenmyhorizon #podcast #thuylinhoi #healing #chualanh #hanhphuc #tamsu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>xe độ chiến</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gi.xinh.vn07/video/7585578507179232532</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7453479097071570184</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>có tất 😏</t>
+          <t>Hy vọng những cặp đôi đang bên nhau sẽ luôn hạnh phúc Những ai chưa tìm được mảnh ghép phù hợp sẽ yêu thương bản thân, giữ gìn sức khoẻ, ăn đủ bữa, ngủ đủ giấc nhennnn 💗</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>#sexy #pinky #gaixinhvn #gaixinh #bikini</t>
+          <t>#alominhngheday #broadenmyhorizon #podcasts #tinhyeu #tamsu #love #xuhuong</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gái Xinh</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gi.xinh.vn07/video/7354352146650828040</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7449306060600413448</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hí, mắc cỡ quá 😁</t>
+          <t>Ngày còn trẻ, có mấy ai mà suy nghĩ được thực tế Lúc trưởng thành, còn mấy ai giám ôm ước mơ to Thành phố mình đang sống thật lớn, thật đẹp, thật hoa lệ, nhưng hoa thì ít mà lệ rơi xuống lại nhiều Cả ngàn lần mình phải tự nhủ "Cố lên, cố hơn nữa đi, nhất định sẽ ổn thôi!" Xa nhà chừng đó năm, các cậu thế nào rồi!</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>#xuhuong #gaixinh #xh #trending</t>
+          <t>#alominhngheday #broadenmyhorizon #truongthanh #podcasts #healing #tamsu #xuhuong</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Gái Xinh</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gi.xinh.vn07/video/7682269563479821588</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7449407810435124498</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dính dính quá ... dính quá 🤭</t>
+          <t>Nếu chuyến đi này là chuyến đi thanh xuân, mình mong chúng ta đều sẽ thật hạnh phúc, và thành công</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>#sexy #gaixinhvn #gaixinhmacpinky #pinky #bikini</t>
+          <t>#alominhngheday #broadenmyhorizon #truongthanh #giadinh #podcasts #tamsu #xuhuong</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Gái Xinh</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gi.xinh.vn07/video/7680415230438034696</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7442924995224947986</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Con chó hay hứa, còn con bò thì hay tin lời con chó 🙂</t>
+          <t>Thi thoảng tui muốn làm người "Hâm" Hâm lắm ý nhưng mà vui, mà tích cực</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>#gaixinhvn #gaixinhmacpinky #sexy #pinky #aohaiday</t>
+          <t>#alominhngheday #broadenmyhorizon #podcast #motivation #lovemyself #healing #fyp #xuhuong</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gái Xinh</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gi.xinh.vn07/video/7679674659930950920</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7352077257768176913</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M thích thì m chan t đê</t>
+          <t>Dáng vẻ học tập, thức khuya dậy sớm ôn bài có khi nào mà không nhếch nhác được cơ chứ Nhưng dáng vẻ khi đỗ đạt, thành công sẽ toả sáng hơn bất cứ thứ gì trên đời này</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>#gaixinhvn #gaixinhmacpinky #sexy #bikini #gymgirl</t>
+          <t>#alominhngheday #broadenmyhorizon #podcast #dodaihoc2024 #2k6 #quyettamdodaihoc #nv1 #motivation #trending #fyp #xuhuong</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Gái Xinh</t>
-        </is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gi.xinh.vn07/video/7680067971204582674</t>
+          <t>https://www.tiktok.com/@alominhngheday/video/7436353456312569096</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thời buổi giờ chỉ cần sống ảo thôi</t>
+          <t>37.2 nghìn tế bào trong cơ thể luôn cố gắng hết mình để bảo vệ chúng ta Vậy điều gì khiến chúng ta phải cảm thấy cô đơn giữa dòng đời này?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>#gaixinhvn #gaixinhmacpinky #sexy #bikini #pinky</t>
+          <t>#alominhngheday #broadenmyhorizon #podcast #motivation #lovemyself #healing #fyp #xuhuong</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alominhngheday/video/7455391368618200338</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tôi yêu Việt Nam Nếu có kiếp nhau - Tôi vẫn muốn là người Việt Nam Việt Nam quyết thắng 🇻🇳🇻🇳🇻🇳</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>#alominhngheday #broadenmyhorizon #vietnam #podcasts #sechienthang #xuhuong</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alominhngheday/video/7346890462365650178</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hai mấy tuổi, mà sao nhiều nỗi sợ thế Sợ mất tiền, mất bạn, mất tình yêu Cơ mà nỗi sợ nào cũng phải vượt qua nếu cậu muốn trưởng thành Rồi cậu sẽ gặp được những cơ hội mới, tìm được những người bạn mới, sẽ có người mới xứng đáng cùng cậu chung đôi Cố lênn</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>#alominhngheday #broadenmyhorizon #motivation #healing #podcast #dongluc #fyp #trening #xuhuong</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alominhngheday/video/7450456709778263303</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>"Mãi nhớ về nhau" "Đừng quên nhau nhé" "Thi thoảng gặp nhau nha" Thử hỏi mấy cái hẹn kia, còn bao nhiêu người trong chúng ta đến đúng hẹn...</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>#alominhngheday #broadenmyhorizon #summer #cuoicap #tamsu #xuhuong</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alominhngheday/video/7341768475230080257</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chúc các cậu - sĩ tử 2k6 Đỗ Nguyện Vọng Một Điểm số thắp sáng bầu trời Tương lai một đường nở hoa Quyết tâm đỗ đại học💪🏻💪🏻💪🏻🏵️🏵️🏵️ quyettamdodaihoc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>#CapCut #alominhngheday #broadenmyhorizon #2k6 #2k6quyettamdodaihoc #nv1 #trending #podcast #xuhuong #fyp</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alominhngheday/video/7448494468736584980</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mùa đông năm cuối cấp còn ngây thơ, ngô nghê và ngốc nghếch Cũng bởi lẽ đó, mà không nhận ra đó là mùa đông cuối cùng được ngồi cùng nhau trong lớp học ấy, được nghe bài giảng ấy và được cười khúc khích vô lo cùng nhau trong những tiết học cuối cùng của một thời áo trắng Gió mùa kéo về, kéo cả những nỗi nhớ thuở còn ngây thơ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>#alominhngheday #broadenmyhorizon #mùađông #hocsinhcuoicap #hoainiem #podcasts #healing #tamsu #xuhuong</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alominhngheday/video/7329908545669958913</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Chúc 2k9 ở chặng cuối sẽ bứt tốc, đạt được kết quả cao trong kỳ thi vào cấp Ba sắp tới nha Hình dáng nỗ lực có thể hơi nhếch nhác, nhưng chắc chắn kết quả sẽ nở hoa onthivao10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>#alominhngheday #broadenmyhorizon #podcast #2k9 #2k9onthivao10 #docap3 #motivation #study #trending #xuhuong</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alominhngheday/video/7326882367988092162</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nếu cậu có một vé xe quay về Ký ức, cậu sẽ chọn nơi nào</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>#alominhngheday #broadenmyhorizon #podcast #cap2 #kyniem #hocsinh #study #healing #trending #xuhuong</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alominhngheday/video/7351825524232277265</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Các sĩ tử 2k6 chắc giờ này còn thức ôn bài, luyện đề nhỉ Chúc các cậu tất cả, sức khoẻ, tâm trí, may mắn - 2k6 nguyện vọng 1 triển!!!!!</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>#alominhngheday #broadenmyhorizon #podcast #2k6 #quyettamdodaihoc #nv1 #motivation #healing #fyp #trending</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alominhngheday/video/7312663633907944705</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Podcast không đề, cuộc gọi không tên, duyên lành của chúng ta đó❤️</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>#podcast #alominhngheday #broadenmyhorizon #kechuyen #healing #motivation #xuhuong #fyp</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7683166106076351752</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cứ Thế - Orange ft Hoang Dung</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>#OrangeSinger #nhachaymoingay #music #fyp #lyrics</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7683726407200935186</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Xoá Tên Em Đi</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>#PHAO #PhaoNorthside #CtrlX</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alominhngheday/video/7328016440412425474</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Thi thoảng rủ nhau đi trộm xoài, trộm ngô, ngô với xoài ở nhà mẹ mua chả thiếu đâu, cơ mà của "hôi" vẫn cứ là ngonnn ý Có ai giống tui không</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>#alominhngheday #broadenmyhorizon #podcast #kyniem #hocsinh #study #healing #trending #xuhuong</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alominhngheday/video/7326159010674265346</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Chúng mình học, để làm gì? Nếu cậu còn thắc mắc, mình kể cậu nghe...</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>#alominhngheday #broadenmyhorizon #podcast #motivation #study #trending</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7682078942643096840</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Chẳng Dám Ngỏ Lời - OST Lửa Trắng</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>#changdamngoloi #mungo #ducanh #betamusic</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alominhngheday/video/7447155534186302741</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Một năm qua của cậu dù thế nào chăng nữa, mong cậu vẫn biết ơn bản thân mình vì đã: Vẫn tồn tại, vẫn sống, vẫn cố gắng Vẫn đi học, đi làm chăm chỉ Tớ tự hào về cậu Cậu cũng hãy tự hào về bản thân thật nhiều nhớ 2024 chuẩn bị đi đến hồi kết, chúc cậu mạnh khoẻ và bình an Gửi đến cậu ngàn cái ôm 💌</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>#alominhngheday #broadenmyhorizon #podcast #cuoinam2024 #healing #tamsu</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alominhngheday/video/7312797089468009730</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trái tim là của cậu, cậu hãy bảo vệ nó ❤️</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>#podcast #alominhngheday #broadenmyhorizon #kechuyen #healing #tinhyeu #Love #trending #fyp</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Góc Nhỏ Podcast</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7681714935109324039</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Phim Hộ Linh Tráng Sĩ nha cả nhà</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>#lunyentertainment #holinhtrangsi</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7681984205760253192</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Anh cũng biết yêu và biết đau buồn mà.. | Vô Hậu Remix</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>#vohau #airmedia</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7679673478017977608</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Chịu Lai Bánh - Hoá Tương Tư Remix - SinKra Remix</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>#nhachaymoingay #music #lyrics #hottrend #fyp</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7676434692320562440</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Gia Đình Chúng Ta - Đức Cảnh Remix</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>#giadinhchungta #DucCanh #nhacremix</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7680522388550782215</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Quên Một Người Từng Yêu - NVT Remix</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>#nhachaymoingay #music #lyrics #hottrend #fyp</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7676075337909898514</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Vẫn Nhớ - Qtrung Remix</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>#nhachaymoingay #music #lyrics #hottrend #fyp</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7677222770228563218</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sớm Nắng Chiều Mưa - Trần Mạnh Cường</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>#lunyentertainment #somnangchieumua #tranmanhcuong #Masew</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7676457375695490311</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Mưa Hạ - Lamoon guiH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>#LAMOON #LAMOONguiH #MUAHA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7675646406232722696</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Tình Sâu Phận Mỏng - Trung Dio</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>#tinhsauphanmong #luytinh2 #trungdio #NDTmedia #BKGroupgital</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7675232873883929874</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Phim Ma Tù nha mọi người</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>#MaTu #GhostInTheCell #BKGroupgital #NDTmedia</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7677558095257619730</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Thích Em Thì Nói Đi - Thoại Nghi</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>#ICMEntertainment #ThoaiNghi #ThichEmThiNoiDi #EPXanhLaXaLanh #Vieent</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7673350404582673682</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>mang bản Việt tới đây cho t</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>#quytuvuotgiau #successor #quytuvuotgiau</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7683946374668340496</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cùng Tel Academy luyện phản xạ giao tiếp tiếng Anh với CÁC CÂU HỎI BẰNG TIẾNG ANH thật tự nhiên nhé! ✨ Học tiếng Anh không chỉ là ghi nhớ kiến thức mà còn là rèn luyện phản xạ để sử dụng trong giao tiếp thực tế mỗi ngày. 👉 Inbox ngay cho Tel Academy hoặc comment để được Ms Nhung tư vấn lộ trình học phù hợp nha!</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #telacademy #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7683854575320698130</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>🎵 Học tiếng Anh qua bài hát – nghe một lần là muốn đọc theo ngay! 🍎🎒🥕🪑 A-A-Apple 🍎 B-B-Bag 🎒 C-C-Carrot 🥕 D-D-Desk 🪑 Vừa hát 🎶 vừa luyện phản xạ với câu hỏi “What’s this?” – cách học đơn giản, vui và dễ nhớ cho người mới bắt đầu. 💛 👉 Cùng Ms Nhung học tiếng Anh mỗi ngày nhé!</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #telacademy #EnglishSpeaking #LuyenPhanXa #TELAcademy #TiengAnhTieuHoc #EnglishForKids #TiengAnhChoTreEm</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7683501990285937937</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>🔤 Âm /aɪ/ đọc thế nào? 🤔 👉 I → /aɪ/ 👉 my → /maɪ/ 👉 time → /taɪm/ 👉 five → /faɪv/ 👉 life → /laɪf/ 👉 try → /traɪ/ 👉 kind → /kaɪnd/ 💡 Gặp những từ này, nhớ bật âm /aɪ/ nhé! 🎯 Xem hết video và thử đọc theo Ms Nhung nào!</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #telacademy #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7683251664194718983</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cùng Tel Academy luyện phản xạ giao tiếp tiếng Anh thật tự nhiên nhé! ✨ Học tiếng Anh không chỉ là ghi nhớ kiến thức mà còn là rèn luyện phản xạ để sử dụng trong giao tiếp thực tế mỗi ngày. 👉 Inbox ngay cho Tel Academy hoặc comment để được Ms Nhung tư vấn lộ trình học phù hợp nha!</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #telacademy #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7683628230225480968</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cùng Tel Academy luyện phản xạ giao tiếp tiếng Anh với cấu trúc PHỦ ĐỊNH - DON’T thật tự nhiên nhé! ✨ Học tiếng Anh không chỉ là ghi nhớ kiến thức mà còn là rèn luyện phản xạ để sử dụng trong giao tiếp thực tế mỗi ngày. 👉 Inbox ngay cho Tel Academy hoặc comment để được Ms Nhung tư vấn lộ trình học phù hợp nha!</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #telacademy #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7683119110401871112</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>🌱 ĐI LÀM NÔNG CŨNG CÓ THỂ HỌC TIẾNG ANH – BẮT ĐẦU TỪ CHÍNH CUỘC SỐNG HẰNG NGÀY! 🇬🇧 Tiếng Anh không nhất thiết phải bắt đầu từ những chủ đề xa lạ. Hãy bắt đầu bằng chính những điều bạn làm mỗi ngày! 💬 Một cuộc hội thoại đơn giản có thể giúp bạn luyện được rất nhiều tình huống giao tiếp thực tế: 👋 Giới thiệu tên và tuổi 📍 Nói mình sống ở đâu 👨‍🌾 Giới thiệu nghề nghiệp 🏡 Nói về nơi làm việc 🌱 Mô tả công việc hằng ngày ⏰ Nói về thời gian bắt đầu làm việc 💡 Điều quan trọng không phải là học thật nhiều từ vựng, mà là biết dùng những câu đơn giản để nói về chính mình. Từ “Tôi tên là…”, “Tôi sống ở…”, “Tôi là…” đến “Tôi bắt đầu làm việc lúc…” — tất cả đều là những mẫu câu có thể sử dụng ngay trong giao tiếp. 🎯 Học điều mình cần – nói điều mình biết – luyện mỗi ngày. Tiếng Anh sẽ trở nên gần gũi và dễ nhớ hơn rất nhiều! 💾 Lưu video lại và luyện nói theo từng câu để hình thành phản xạ nhé! 💙</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #telacademy #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ilovelyrics08/video/7675811701584891143</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>chúc mừng kênh tròn 1 tuổi 🎂 (20/8/2025 - 20/8/2026)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>#happybirthday #kiniem #ilovelyrics #fyp #xuhuong</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>𝘼𝙧𝙞𝙨 𝙈𝙪𝙨𝙞𝙘</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7682747303337282823</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>⏰ MẤY GIỜ RỒI? NÓI GIỜ BẰNG TIẾNG ANH KHÔNG KHÓ! Bạn có hay bị khựng lại khi ai đó hỏi “What time is it?” không? 👀 Chỉ cần nắm vài cách nói cơ bản là có thể đọc giờ cực tự nhiên rồi! 🕖 7:00 → It’s seven o’clock 👉 o’clock dùng khi nói giờ đúng. 🕢 7:15 → It’s seven fifteen / A quarter past seven 👉 a quarter past = hơn 15 phút. 🕣 7:30 → It’s seven thirty / Half past seven 👉 half past = hơn 30 phút. 🕗 7:45 → It’s seven forty-five / A quarter to eight 👉 a quarter to = còn 15 phút nữa đến giờ tiếp theo. 📌 Mẹo nhớ siêu nhanh: ✨ o’clock → giờ đúng ✨ past → hơn ✨ to → kém ✨ a quarter → 15 phút ✨ half → 30 phút 🎯 Học theo quy luật thay vì học thuộc từng câu, bạn sẽ có thể tự đọc rất nhiều mốc giờ khác nhau! 💾 Lưu video lại để lần sau nhìn đồng hồ là nói được ngay bằng tiếng Anh nhé! ⏰💙</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7682476838219697416</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cùng Tel Academy luyện phản xạ giao tiếp tiếng Anh với chủ đề FOOD AND DRINK - ĐỒ ĂN THỨC UỐNG thật tự nhiên nhé! ✨ Học tiếng Anh không chỉ là ghi nhớ kiến thức mà còn là rèn luyện phản xạ để sử dụng trong giao tiếp thực tế mỗi ngày. 👉 Inbox ngay cho Tel Academy hoặc comment để được Ms Nhung tư vấn lộ trình học phù hợp nha!</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7681628660251561224</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>🗣️ /ʃ/ – /s/ – /ʒ/ – /z/: 4 ÂM NÀY, BẠN ĐANG ĐỌC ĐÚNG CHƯA? 👀 Đều là những âm rất quen thuộc trong tiếng Anh, nhưng chỉ cần phát âm sai một chút là từ có thể “đổi nghĩa” ngay! 😵‍💫 👄 /ʃ/ – âm “sh”, môi hơi tròn 💨 /s/ – âm “xì”, luồng hơi mạnh 🔊 /ʒ/ – âm “gi” mềm, có rung 🐝 /z/ – âm “z”, có rung 📌 Bí quyết: đừng chỉ nhìn khẩu hình – hãy cảm nhận độ rung ở cổ họng và luồng hơi khi phát âm. Xem video, nghe thật kỹ và đọc theo từng cặp âm để tai quen – miệng chuẩn – nói tự nhiên hơn nhé! 🎧✨ 💾 Lưu video lại để luyện phát âm mỗi ngày!</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7682127784612793607</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Cùng Tel Academy luyện phản xạ giao tiếp tiếng Anh với tình huống GỌI ĐỒ Ở QUÁN CÀ PHÊ thật tự nhiên nhé! ✨ Học tiếng Anh không chỉ là ghi nhớ kiến thức mà còn là rèn luyện phản xạ để sử dụng trong giao tiếp thực tế mỗi ngày. 👉 Inbox ngay cho Tel Academy hoặc comment để được Ms Nhung tư vấn lộ trình học phù hợp nha!</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7681982000529542408</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>🗣️ HỌC TIẾNG ANH QUA 1 VẦN – ĐỌC MỘT LẦN, NHỚ CẢ LOẠT TỪ! ✨ Chỉ cần nắm được âm cuối -ink /ɪŋk/, bạn có thể luyện phát âm cả một nhóm từ cực nhanh! 👀 🖊️ ink – mực 💕 pink – màu hồng 🚰 sink – bồn rửa 🔗 link – liên kết 😉 wink – nháy mắt 🤔 think – nghĩ 🥤 drink – uống ✨ blink – chớp mắt Điểm chung là phần -ink đều có âm /ɪŋk/. Vì vậy thay vì học từng từ một cách rời rạc, hãy luyện theo nhóm âm/vần để miệng quen khẩu hình và tai quen với cách phát âm hơn. 🎧 📌 Mẹo luyện: Đọc chậm → đọc rõ âm /ɪŋk/ → sau đó tăng tốc và đọc liên tục cả nhóm từ. ink → pink → sink → link → wink → think → drink → blink 🔥 💾 Lưu video lại và thử đọc theo 3 lần. Xem lần 3 có nhanh hơn lần 1 không nha! 😆</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa #TELAcademy #TiengAnhTieuHoc #EnglishForKids #TiengAnhChoTreEm</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7681376134898044167</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cùng Tel Academy luyện phản xạ giao tiếp tiếng Anh với mẫu câu giao tiếp TỪ CHỐI thật tự nhiên nhé! ✨ Học tiếng Anh không chỉ là ghi nhớ kiến thức mà còn là rèn luyện phản xạ để sử dụng trong giao tiếp thực tế mỗi ngày. 👉 Inbox ngay cho Tel Academy hoặc comment để được Ms Nhung tư vấn lộ trình học phù hợp nha!</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7681272614479957266</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>🎤 DÂN SALES MUỐN GIAO TIẾP VỚI KHÁCH NƯỚC NGOÀI – HỌC NGAY BÀI NÀY! 💼🌍 Làm sales nhưng mỗi khi gặp khách nước ngoài lại bí từ, không biết giới thiệu bản thân thế nào? 😥 Đừng học tiếng Anh một cách lan man! Hãy bắt đầu từ chính những tình huống bạn gặp mỗi ngày: 💬 Giới thiệu bản thân 📦 Giới thiệu sản phẩm 🙋‍♀️ Tư vấn và giải đáp thắc mắc 🤝 Giao tiếp với khách hàng 🌍 Tự tin trò chuyện với khách nước ngoài 🎵 Biến cả một bài giới thiệu thành một bài hát dễ nhớ, dễ học và dễ nói. 📌 Lưu video lại, thay tên – tuổi – công việc – sản phẩm của bạn vào và thử tự giới thiệu bằng tiếng Anh ngay hôm nay! Sales giỏi không chỉ là bán được hàng, mà còn là biết cách giao tiếp để khách hàng tin tưởng mình. 💙</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7682342869637549330</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>🗣️ LUYỆN PHẢN XẠ TIẾNG ANH CÙNG MS NHUNG &amp; MS WANG! 💬✨ Biết từ vựng và ngữ pháp là một chuyện, nhưng nghe câu hỏi là phải bật ra câu trả lời thật nhanh mới là phản xạ giao tiếp! 🔥 Cùng 2 cô luyện những câu hỏi quen thuộc trong giao tiếp hằng ngày: 🌍 Where are you from? 👩 Where is she from? 👀 Who is that? 👭 How many sisters do you have? 💼 What is her job? 🏢 Where do they work? 📌 Đừng chỉ học thuộc câu hỏi – hãy nghe, hiểu, phản hồi và nói thành tiếng. Luyện đủ nhiều, bạn sẽ dần hình thành phản xạ mà không cần mất thời gian dịch từng câu trong đầu. 🎯 Nghe câu hỏi → hiểu ý → bật câu trả lời → nói tự nhiên! 💙 Cùng Ms Nhung &amp; Ms Wang luyện mỗi ngày để tiếng Anh không còn là những câu học thuộc lòng, mà trở thành ngôn ngữ bạn có thể sử dụng thật sự!</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7680519024358247688</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>🎤 BÀI HÁT GIỚI THIỆU BẢN THÂN BẰNG TIẾNG ANH ✨ Muốn tự tin giới thiệu bản thân nhưng mỗi lần nói lại không biết bắt đầu từ đâu? 👀 Hãy biến những câu giới thiệu cơ bản thành một bài hát dễ nhớ, dễ nói và dễ luyện phản xạ! 🎵 Từ tên tuổi → nghề nghiệp → công việc → mục tiêu học tiếng Anh, bạn hoàn toàn có thể tự giới thiệu về mình một cách tự nhiên và tự tin hơn. 💙 Học thuộc bài hát → nhớ mẫu câu 🗣️ Hát theo → luyện phát âm 🔁 Lặp lại → tăng phản xạ giao tiếp 📌 Lưu video và thử thay thông tin của bạn vào để tạo bài giới thiệu của riêng mình nhé!</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7682893666947534098</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cùng Tel Academy luyện phản xạ giao tiếp tiếng Anh với tình huống KHI ĐANG BẬN thật tự nhiên nhé! ✨ Học tiếng Anh không chỉ là ghi nhớ kiến thức mà còn là rèn luyện phản xạ để sử dụng trong giao tiếp thực tế mỗi ngày. 👉 Inbox ngay cho Tel Academy hoặc comment để được Ms Nhung tư vấn lộ trình học phù hợp nha!</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7680992597493452040</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Cùng Tel Academy luyện phản xạ giao tiếp tiếng Anh với mẫu câu giao tiếp CẢM ƠN thật tự nhiên nhé! ✨ @ Học tiếng Anh không chỉ là ghi nhớ kiến thức mà còn là rèn luyện phản xạ để sử dụng trong giao tiếp thực tế mỗi ngày. 👉 Inbox ngay cho Tel Academy hoặc comment để được Ms Nhung tư vấn lộ trình học phù hợp nha!</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7680277015185919240</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Cùng Tel Academy luyện phản xạ giao tiếp tiếng Anh TÍNH TỪ SỞ HỮU thật tự nhiên nhé! ✨ Học tiếng Anh không chỉ là ghi nhớ kiến thức mà còn là rèn luyện phản xạ để sử dụng trong giao tiếp thực tế mỗi ngày. 👉 Inbox ngay cho Tel Academy hoặc comment để được Ms Nhung tư vấn lộ trình học phù hợp nha!</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7681758993915579655</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cùng Tel Academy luyện phản xạ giao tiếp tiếng Anh tự nhiên nhé! ✨ Học tiếng Anh không chỉ là ghi nhớ kiến thức mà còn là rèn luyện phản xạ để sử dụng trong giao tiếp thực tế mỗi ngày. 👉 Inbox ngay cho Tel Academy hoặc comment để được Ms Nhung tư vấn lộ trình học phù hợp nha!</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7679383833959025940</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>🤝 LẦN ĐẦU GẶP NHAU, NÓI GÌ BẰNG TIẾNG ANH? 🎵 Lần đầu gặp một người nước ngoài mà không biết mở lời thế nào? Đừng lo! Hãy bỏ túi ngay những cụm từ giao tiếp cơ bản này và luyện qua bài hát để nhớ lâu hơn. 💬✨ Từ chào hỏi → giới thiệu bản thân → làm quen → kết thúc cuộc trò chuyện, tất cả đều có thể trở thành phản xạ nếu bạn luyện thường xuyên. 🎧 Học qua giai điệu 🗣️ Hát theo từng câu 🔁 Lặp lại mỗi ngày 💙 Tự tin hơn trong lần gặp đầu tiên! 📌 Lưu video lại để lần sau gặp người mới không còn “đứng hình” nhé! 😆</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7679142413419482375</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Cùng Tel Academy luyện phản xạ giao tiếp tiếng Anh cấu trúc NÓI VỀ QUÊ QUÁN thật tự nhiên nhé! ✨ Học tiếng Anh không chỉ là ghi nhớ kiến thức mà còn là rèn luyện phản xạ để sử dụng trong giao tiếp thực tế mỗi ngày. 👉 Inbox ngay cho Tel Academy hoặc comment để được Ms Nhung tư vấn lộ trình học phù hợp nha!</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7679919358503668999</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Cùng Tel Academy luyện phản xạ giao tiếp tiếng Anh thật tự nhiên nhé! ✨ Học tiếng Anh không chỉ là ghi nhớ kiến thức mà còn là rèn luyện phản xạ để sử dụng trong giao tiếp thực tế mỗi ngày. 👉 Inbox ngay cho Tel Academy hoặc comment để được Ms Nhung tư vấn lộ trình học phù hợp nha!</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7678644475777813768</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>🗣️ LUYỆN NỐI ÂM TIẾNG ANH – NÓI TỰ NHIÊN HƠN MỖI NGÀY! 🎧 Tại sao người bản xứ nói tiếng Anh nghe liền mạch và nhanh hơn khi đọc từng từ? 👀 👉 Vì họ sử dụng nối âm! Cùng luyện nối âm qua những cụm câu quen thuộc: ✨ I like it. ✨ Pick it up. ✨ Take it. ✨ Take off. ✨ Look at it. 🎯 Đừng đọc từng từ một! Hãy thử nối các âm lại với nhau, bắt chước đúng nhịp và ngữ điệu để câu nói trở nên tự nhiên hơn. 🎧 Nghe → nối âm → bắt chước → lặp lại Lưu video và luyện mỗi ngày để tiếng Anh của bạn ngày càng mượt và tự nhiên hơn nhé! 💙</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7678625536054168850</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Cùng Tel Academy luyện phản xạ giao tiếp tiếng Anh tình huống HỎI VỀ BỮA ĂN thật tự nhiên nhé! ✨ Học tiếng Anh không chỉ là ghi nhớ kiến thức mà còn là rèn luyện phản xạ để sử dụng trong giao tiếp thực tế mỗi ngày. 👉 Inbox ngay cho Tel Academy hoặc comment để được Ms Nhung tư vấn lộ trình học phù hợp nha!</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7680134719383637255</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>🏃‍♀️⚽ PLAY + MÔN THỂ THAO | GO + V-ING 🎯 Nói về các hoạt động thể thao bằng tiếng Anh mà hay bị nhầm play và go? Nhớ ngay 2 công thức này! 👇 ⚽ PLAY + môn thể thao → play football → play tennis → play badminton → play basketball 🏃 GO + V-ing → go swimming → go running → go cycling → go hiking 💡 PLAY thường đi với tên môn thể thao, đặc biệt là các môn có tính đối kháng/trò chơi. GO + V-ing thường dùng để nói về hoạt động thể chất, giải trí. 📚 Học đúng cấu trúc → đặt câu nhanh hơn → giao tiếp tự nhiên hơn! Lưu video để ôn lại khi cần nhé! 💙</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7683453845166492946</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Chồng chỉ việc kiếm tiền mang về còn đối tác của chồng để vợ lo. Dạ dày vui thì hợp đồng trộm vía lắm!</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #umuoihoatieu #nauancungtiktok #monngonmoingay</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@englishforeveryone72/video/7679015873138511112</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>TOP OF THE WORLD 🌎✨ Một giai điệu quen thuộc, một cách học tiếng Anh thật nhẹ nhàng! 💙 Học tiếng Anh qua Top of the World để vừa thư giãn, vừa luyện kỹ năng nghe, phát âm, ngữ điệu và làm quen với cách diễn đạt tự nhiên trong tiếng Anh. 🎧 Nghe nhiều hơn 🗣️ Hát theo nhiều hơn 🌱 Luyện tập mỗi ngày ✨ Tự tin hơn từng chút một Học tiếng Anh qua âm nhạc – để mỗi bài hát trở thành một bài học! 💙 Lưu ngay video để luyện tập mỗi ngày cùng Ms Nhung nhé!</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>#msnhungtelacademy #hocgiaotiepcungtelacademy #learnenglisheveryday #hoctienganhgiaotiep #30ngayvuotnguongchinhphuctienganh #telacademy #TiengAnhGiaoTiep #HocTiengAnh #LearnEnglish #EnglishSpeaking #LuyenPhanXa</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Học Tiếng Anh Cùng Tôi</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7681971310175538450</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Thêm 1 món mà không biết hôm nay ăn gì nữa thì triển luôn món này. Ngon bổ rẻ nhanh tiện đủ cả</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #nauancungtiktok #monngonmoingay #ancungtiktok</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7681240855289613576</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Vừa đẹp vừa ngon luôn ạ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #monngonmoingay #nauancungtiktok #ancungtiktok</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7678633019636452615</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Canh này không ngọt thì còn canh nào ngọt?</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #monngonmoingay #nauancungtiktok #ancungtiktok</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7679004395035528456</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Nghe nói măng xào với lá gừng ngon lắm!</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #monngonmoingay #nauancungtiktok #ancungtiktok</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7677894923768565000</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Khoai tây mà lại mang xào với thì là, thì là………ngon chứ sao!</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #monngonmoingay #nauancungtiktok #ancungtiktok</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7677877403208748296</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Quà chiều món này hợp lí không các bác?</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #monngonmoingay #nauancungtiktok #ancungtiktok</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7679373835488988424</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Cá gì đã đẹp còn ngon? Nấu canh chua hay rán trứng thì tuyệt cà là vời</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #monngonmoingay #nauancungtiktok #ancungtiktok</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7678257327803206930</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ngon luôn!</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #monngonmoingay #nauancungtiktok #ancungtiktok</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7677137624401792263</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Đơn giản mà ngon</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #ancungtiktok #monngonmoingay #nauancungtiktok</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7677060391196724498</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cuối tuần làm tí mồi bén cho gia đình quây quần</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #ancungtiktok #monngonmoingay #nauancungtiktok</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7677572003150253330</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Mướp luộc muốn giữ được độ ngọt mà không bị úng nước chỉ cần biết 1 mẹo nhỏ này thôi.</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #ancungtiktok #monngonmoingay #nauancungtiktok</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7684123826074209554</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Lâm lần đầu chạm mặt William Gurgui - bài toán quốc tế thứ hai của anh ở sân chơi MMA Pro 🤷🏻</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>#lionchampionship2026 #LIONChampionship #LC35 #mma #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7676767248836545800</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Cứ không nghĩ ra ăn gì thì lại ăn món này. Nhanh gọn lại ngon các bác ạ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #monngonmoingay #ancungtiktok #nauancungtiktok</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7674178888032931080</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Vừa ngon vừa đẹp thấy là muốn động đũa liền</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #ancungtiktok #monngonmoingay #umuoihoatieu</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7676022356170624274</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Suýt xoa</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #ancungtiktok #monngonmoingay #micay</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7683825544185531656</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BIẾN ĐAU THƯƠNG THÀNH SỨC MẠNH! Phải trải qua sự mất mát quá lớn ngay trước trận ra mắt MMA Pro, nhưng Lê Công Nghị vẫn nén lại nỗi buồn để thể hiện một màn trình diễn đẳng cấp, qua đó dành tặng một món quà ý nghĩa cho người mẹ trên thiên đường của mình. Anh sẽ xuất hiện trong trận đấu tâm điểm tại LC35 vào cuối tuần này gặp Nguyễn Phú Thịnh để hướng tới một suất tranh đai ở hạng 52kg!</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>#LC35 #LIONChampionship #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7684119677286501639</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Lê Công Nghị và Nguyễn Phú Thịnh đứng trước cơ hội tranh đai hạng 52kg vào năm sau 🔥</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>#lionchampionship2026 #LIONChampionship #LC35 #mma #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7683379301361782024</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>William Gurgui đã sẵn sàng mang kinh nghiệm chinh chiến quốc tế bước vào LC35, nơi Nguyễn Văn Lâm đang chờ đợi anh trong cuộc đối đầu ở hạng cân 65kg 👊</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>#lionchampionship2026 #LIONChampionship #LC35 #mma #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7679008545060244756</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Lời xin lỗi của Hồ Hồng Tường và Hải Lạp Bố Tát - hai thành viên còn lại của ban huấn luyện đội Trung Quốc đã tự ý xâm nhập vào khu vực thi đấu, gây ra vụ ẩu đả tại YFU 96 và đã phải nhận án phạt cấm thi đấu trong toàn bộ hệ thống giải của WLF.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>#LIONChampionship #LIONxYFU</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7683092900720446740</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Cựu vô địch hạng 60kg Nguyễn Trần Duy Nhất đã gọi tên từng võ sĩ sở hữu "nguyên liệu" xuất sắc nhất LION Championship. Liệu cậu học trò Trần Minh Trung mà anh trực tiếp rèn giũa bằng công thức riêng có thể vượt ải Bùi Văn Hùng để nối dài mạch bất bại của No.1 Muay Club trong năm nay?</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>#lionchampionship2026 #LIONChampionship #LC35 #mma #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7681164581632232725</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Một cột mốc mới đang chờ đợi “Luffy” Nguyễn Ngọc Phú khi anh sẽ chính thức có màn ra mắt tại ONE Fight Night 47, đối đầu với võ sĩ đến từ Maroc trong chuyến xuất ngoại tới Bangkok vào Thứ Bảy tuần này (ngày 5/9). Cùng LION Championship tiếp lửa cho đại diện Việt Nam sẽ thi đấu bùng nổ và mang chiến thắng trở về 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>#lionchampionship2026 #LIONChampionship #mma #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7679008275811142933</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Lời xin lỗi của Bạch Lâm Ba - một trong những thành viên của ban huấn luyện đội Trung Quốc đã tự ý xâm nhập vào khu vực thi đấu và gây ra vụ ẩu đả tại YFU 96. Thông cáo chính thức của LION Championship và văn bản xử phạt các cá nhân liên quan của YFU sẽ được công bố vào 21h hôm nay (giờ Việt Nam).</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>#LIONChampionship #LIONxYFU</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7673721529544510740</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Trần Ngọc Lâm dường như muốn nếm thử chút "tiết" của Huỳnh Ngọc Tín chăng? 🩸</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>#LIONChampionship #LC34 #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7673717950867623188</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>VÕ TIẾN ĐẠT ĐÙA KHÔNG VUI, LÊ HOÀNG ĐỨC ĐÃ CĂNG 🤡</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>#lionchampionship2026 #LIONChampionship #LC34 #mma #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7673893314537458951</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Võ Nguyễn Ngọc Linh giữ sự lạnh lùng tuyệt đối và đáp trả ngắn gọn, bất chấp những lời nói từ Tạ Mai Hương 🥶</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>#LIONChampionship #LC34 #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuquynh_95/video/7674917771184016648</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tự là gà rán kfc tại nhà mà ngon cỡ này thì còn ra hàng quán làm gì nữa.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>#xuhuong #quynhquynhthichnaunuong #kfc #garan #ancungtiktok</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Tập Nấu Ăn</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7673897618480696597</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>"Thần Lâm" và Huỳnh Ngọc Tín vẫn không nhường nhau bất cứ một mét vuông nào 🥵</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>#LIONChampionship #LC34 #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7671193124521118997</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>"CHẮC CHẮN SẼ CÓ DOG FIGHT"👇 Lịch sử đang đứng về phía Kickfit Sport MMA khi các chiến binh của họ chưa từng bị hạ gục trước No.1 Muay Club - CLB đang giữ thành tích bất bại trong năm 2026. Khi ngôi vô địch và suất vào thẳng nhóm 2 trên bảng xếp hạng MMA Pro được đặt lên bàn cược, bất kể thống kê nào cũng có thể sụp đổ. Khán giả hoàn toàn có quyền chờ đợi vào màn đôi công mãn nhãn và đầy cống hiến mà Nguyễn Thế Linh đã hứa hẹn sẽ phô diễn tại LC34 sắp tới.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>#lionchampionship2026 #LIONChampionship #LC34 #mma #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7666017450747497748</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>HẠNG 70KG HÃY CHUẨN BỊ ⚠️ Vừa đặt chân đến cánh rừng mới nhưng Phạm Thanh Ngân đã rất nóng lòng khởi động cuộc đi săn của mình. Sự xuất hiện này đủ khiến hạng 70kg sôi sục, ai sẽ là mục tiêu đầu tiên trong tầm ngắm của tay đấm The Champ MMA?</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>#lionchampionship2026 #LIONChampionship #mma #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7663069501281324309</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>KHI NHÀ THI ĐẤU BỊ THỔI BUNG NÓC 🥳 Cận cảnh pha kết thúc bùng nổ của Nguyễn Hữu Hân, từ góc nhìn sát nhất có thể! LC33: Full Highlights Camera Trọng Tài đã phát sóng trên kênh chính thức của LION Championship.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>#LIONChampionship #LC33 #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7663422999688793364</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CHIẾN ĐẤU HẾT MÌNH, TÔN TRỌNG TUYỆT ĐỐI 🫡 Sau ca phẫu thuật của Sa Mã Dĩ Cách, Nguyễn Thành Thoan cùng CLB Raptor MMA đã gửi lời hỏi thăm, động viên và chúc đại diện Trung Quốc sớm hồi phục. Khép lại những phút giây căng thẳng trên lồng bát giác, sự tôn trọng dành cho đối thủ luôn còn ở lại sau tiếng chuông mãn cuộc.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>#lionchampionship2026 #LIONChampionship #LC33 #mma #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7672298993233186068</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>YFU vs LION: CUỘC TÁI NGỘ ĐÁNG MONG CHỜ 🤜🤛 Sáu đại diện của LION Championship trong đó có nhà vô địch hạng cân 60kg Trần Ngọc Lượng sẽ bước vào chuyến làm khách đầy thử thách tại Trịnh Châu, Trung Quốc trong khuôn khổ sự kiện YFU 96 giữa . Chờ đợi họ là những võ sĩ ưu tú nhất của đấu trường YFU trực thuộc giải đấu Wu Lin Feng, một trong những thương hiệu võ thuật hàng đầu Trung Quốc. Hãy cùng LION Championship tiếp lửa cho các đại diện Việt Nam sẽ có những màn thượng đài bản lĩnh, kiên cường vì màu cờ sắc áo vào ngày 22/8 tới.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>#YFUvsLION #lionchampionship2026 #LIONChampionship #mma #TheLIONEra #YFUvsLION</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7665667657726954772</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Tham chiến trong trận đấu chính là mơ ước của nhiều tay đấm. Nhưng nỗi lo duy nhất của "boy phố" Tiến Đạt lại là… cơn buồn ngủ 🥱</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>#lionchampionship2026 #LIONChampionship #LC34 #mma #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7661966802678746389</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>HLV Nguyễn Trần Duy Nhất vui mừng vì cậu học trò Trần Minh Trung có chiến thắng knockout chóng vánh và cực kỳ đẹp mắt 💥</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>#LIONChampionship #LC33 #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7670450650408389909</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CHUNG KẾT STRIKING MỚI CHỈ LÀ SỰ KHỞI ĐẦU 😳 Nguyễn Thế Linh đã lên sẵn một chặng đường với đích đến rất rõ ràng cho bản thân mình ở hạng 60kg MMA Pro. Nhưng tất nhiên, trước đó anh sẽ cần phải vượt qua được Lương Thành Phúc trong một trận chiến cực kỳ căng thẳng tại LC34.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>#lionchampionship2026 #LIONChampionship #LC34 #mma #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7661962044693875988</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Trả lại Thẩm Long cả gốc lẫn lãi, Nguyễn Hữu Hân vẫn khá bình thản sau khi thu phục thành công “con rồng” thứ 2 😅</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>#LIONChampionship #LC33 #TheLIONEra #LIONvsWLF</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7683940538407570708</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Ngân ơi Ngân</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7662365720071752980</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>TÀU LƯỢN CẢM XÚC 🎢 Đó là những gì mà ban huấn luyện của cả Bạch Văn Nghĩa và Danh Quốc được trải qua trong 5 phút đầu tiên của màn chạm trán kinh điển giữa họ - nơi mà đôi bên đều tưởng như đã rất gần một pha kết thúc chấn động.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>#LIONChampionship #LC33 #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7683209160984415508</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>bỏ đi Ngân</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7683598489707760916</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Ngựa OB55 lại bá rồi</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7683438332499512596</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>nay tha Ngân bữa</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>#VoDienFreeFire #nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7683023160060415252</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Ai muốn được a Gà thương giống tui hông</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>#VoDienFreeFire #nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7682698409853209877</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>cái này mới nè</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7661965518470974740</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Thoan ấn tượng với sự lì lợm của Sa Mã Dĩ Cách trong trận đấu hay nhất LC33 👊</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>#LIONChampionship #LC33 #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7683008163238497556</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ngân ơi Ngân</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>#VoDienFreeFire #nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7681487989171588372</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>quá khứ của À húuuu</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7661963347256003860</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Bạch Văn Nghĩa tự tin hướng đến trận tranh đai vô địch sau khi đánh bại Danh Quốc bằng chính sở trường của đối thủ 👏</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>#LIONChampionship #LC33 #TheLIONEra</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LION championship</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7681955360210455828</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Cây DE chết tiệt</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7682085255875939604</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Nói nghe cái chấn động luôn</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7681354759949028628</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>để t đấm là ăn rồi</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #free_fire #freefire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7680233646665616661</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>hay quá bạn ơi🤣</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7680464612294266132</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Sinh tồn lúc này</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7680070100094881044</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>m thấy hối hận chưa?</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7681742141395094804</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Cao nhân nào edit dùm đoạn này cho ngầu ngầu với 🤣</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7679725960643530004</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ok xả stress</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7679516398774668564</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>lại là con Ngân</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7678975315334466837</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>trung bình con Ngân khi chơi game</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7681019307089759508</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>À húuuu</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #free_fire #freefire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7679121788760083732</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Ai edit dùm đoạn này cho ngầu ngầu với🤣</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7679358783004396820</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>đầu đá 🗿</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7679888294494211349</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Gan trời rồi</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7678387689237875989</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Cái này mới nè</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7678811684189785364</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Thôi xong,ẩu quá cốt 🤣 phần cuối</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7677868074028027157</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Cảm mơn mọi người..</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #trendff #xuhuong</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7529051646786096402</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Chế độ gì đây anh em❓</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>#XeĐộ #XeKiểng #XeDrag #ĐộXe #racing</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7529463755202120968</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Xe gì nhìn lạ quá anh em😂</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>#XeĐộ #ĐộXe #BikerVN #XeDrag #racing #XeKiểng</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7678636007595494676</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Phần 2 : Chối rồi , chối rồi</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7677931745164954900</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>những cái Lốp tệ nhất</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #trendff #xuhuong</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7683772193741868309</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>🛞Form lùn gần đụng đất cho anh em thích trưng🛠️ 🦁Dáng mã – 76jet8 – Gần full option💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7683388035744156948</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>🛞Check xong mọi thứ chờ ngày lên đường qua Mỹ nha🛠️ 🦁Dáng mã – 76jet10 – Dọn full new💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7683525643136601364</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>🛞Vừa về con xe anh em chơi là có xe trong ngày nha🛠️ 🦁Dáng tour – 72jet4 – Kiểng nhẹ keng nha💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7684133808941124885</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>🛞Chuẩn bị hoàn thiện con xe dễ tiếp cận🛠️ 🦁Dáng mã – 68jet6 – Cơ bản gọn gàng💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7680837052631485716</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>cứu tôi</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7683879400386923796</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>🛞Dọn chi tiết là như này nha🛠️ 🦁Dáng mã – 72jet8 – Full new full real💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7678024453757963540</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>thà mất mạng chứ không để mất kill</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #trendff #xuhuong</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theshy2004/video/7678241739517267220</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>thôi xong,ẩu quá cốt</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>#nhasangtaofreefire #freefire #free_fire #xuhuong</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7682653891154021652</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>🛞Chuẩn bị qua Mỹ theo anh trai nhanh gọn🛠️ 🦁Dáng mã – 76jet10 – Dọn từ sườn dọn ra💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7682406790557879572</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>🛞Con xe đi phố cafe ít đụng hàng nha🛠️ 🦁Fuled – 65jet3 – Full otpion real💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7683122156988943636</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>🛞Vừa thử nghiệm Đà Nẵng quay đầu vẫn êm nha🛠️ 🦁Dáng tour – 65zz – pô êm zin – Full option💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7683025536599280916</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>🛞Con xe trưng kiểng hay chơi nhẹ nhàng đều được nha🛠️ 🦁Dáng mã – 76jet8 – Dàn chân còn keng nha💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7682781925026614549</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>🛞Form xe gọn gàng cơ bản dễ tiếp cận🛠️ 🦁Dáng mã – 72jet4 – hoàn thiện là lên sóng lại nha💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7681667738275925268</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>🛞Form malay lùn gần chạm đất🛠️ 🦁Dáng mã – 76jet8 – Full real💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7681539262713548052</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>🛞Mời anh em tìm món đồ cũ trên con xe này🛠️ 🦁Dáng mã – 72jet8 – Full real full new💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7681181325960744213</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>🛞Trưng đủ mẫu đủ cấu hình cho anh em lựa⚒️ 🦁Dáng mã – Dáng tour – Sườn nhôm – Drag💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing #drag</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7680428373436370196</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>🛞Mình cần thu thêm mấy form như này nha anh em🛠️ 🦁Dáng mã – 79jet12💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7680815215210024213</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>🛞Bài này nhiều anh em hay hỏi nha🛠️ 🦁Dáng mã – 72jet4 – Cơ bản gọn gàng💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7680550588043627796</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>🛞Anh em nào tìm form xe như này thì đây nha🛠️ 🦁Dáng mã – 76jet8 – Full kiểng💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7681913428285508885</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>🛞Mỗi xe mỗi phong cách🛠️ 🦁Dáng mã – 76jet10 &amp; Dáng mã – 72jet8 – Full new full real💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7682024746757721365</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>🛞Trưng kiểng thì yên tĩnh mà cất tiếng thì như này nha🛠️ 🦁Dáng mã – Dáng tour – Sườn nhôm – Drag💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing #drag</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7679794570368126229</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>🛞Con xe đáng để chơi hoặc trưng kiểng nha🛠️ 🦁Dáng mã – 72jet8 – dọn full new full real💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7679689998009978132</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>🦁Con xe cho anh em mới chơi trải nghiệm💥 🛞Sườn nhôm – 65+ – Demo cho anh em xem🛠️ 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7679414526365764885</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>🛞Xe nhà dọn là như này nha anh em🛠️ 🦁Dáng tour – 74jet8 – Gần full new💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7682282651968916757</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>🛞Demo cho anh em xem trước con xe đang dọn nha🛠️ 🦁Dáng tour – 74jet8 – Full new full real💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7679067129169087765</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>🛞Lên đường một cặp hai dáng nha🛠️ 🦁Dáng mã – 79jet12 &amp; Dáng tour – 72jet8💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7681305985620725013</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>🛞Xe dọn mà lực thì có con này nha🛠️ 🦁Dáng mã – 76jet10 – Full kiểng gần new nha💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7678945437650406677</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>🛞Mình cần thu thêm mấy form như này nha🛠️ 🦁Dáng mã – 79jet12 – Cơ bản💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7680070601372912917</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>🛞Trưng vài con từ cơ bản đến full đồ cho anh em dễ tham khảo🛠️ 🦁Dáng tour – 65zz ➡️ 82jet8💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7678698742559640853</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>🛞Hoàn thiện lên đường trong ngày nha🛠️ 🦁Dáng mã – 79jet12 – Cơ bản gọn gàng💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7204057438906109230</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #xuhuong</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
           <t>Gái Xinh</t>
         </is>
+      </c>
+      <c r="E171" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7199605448771783978</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7197006316668292398</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7195517423552941355</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>buổi tối vui vẻ 💃</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7287934807777185070</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>cho em xin ít tym đi mà😊 china douyin</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>#gaixinh #gaixinhchina #gaixinhdouyin #trending #xuhuong #warehouseupl</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7198155045098032430</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>♻️ 💃</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #xuhuong</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7191437789907504430</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Trả lời @khoa_khon_kheo cung hỷ phát tài 💃</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #tetmaiman</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7193288209676209450</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #HoiHanKipKhong</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7203314854118034734</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #xuhuong</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7191297861575920942</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Trả lời @thanhbhc006 🥰 💃</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #tetmaiman</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7192189119416552747</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #tetmaiman</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7190896876378688814</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #tetmaiman</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@dip.lm.huy.dlk.te/video/7679316348958248212</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>🛞Con xe tâm huyết giờ nên đi tour đâu đây🛠️ 🦁Dáng tour – 72jet5 – Full option real💥 🇻🇳</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>#xedovietnam #ex150_style_malay #ex150độkiểng #racing</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>xe độ chiến</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7189593936166473002</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7188115543365471534</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7194410044224490798</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #xuhuong #HoiHanKipKhong</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7188836068999957802</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7185514891971956014</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>💕💕💕 💃</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #xuhuong2023 #xuhuong</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7187357368680729898</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7184016448103157035</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #xuhuong2023 #xuhuong</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7186612789081853227</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7183471518540631342</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>hello 2023 🥰 💃</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #trending #girls #fyp #xuhuong2023</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7180691846048337194</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #fyp #girls #trending #GiangSinh2022</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7179973302281096494</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>#gaixinh #gaixinh #nhaycungtiktok #xuhuong2022 #fyp #girls #trending #GiangSinh2022</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7182902356269485354</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #trending #affcup2022</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7182527325576252715</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>💃</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #xuhuong2022 #fyp #girls #trending #xuhuong</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_uocxuhuongtiktok_/video/7184757825896434990</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>💃 2022 2023</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>#gaixinh #nhaycungtiktok #trending #xuhuong #xuhuong2022 #xuhuong2023</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/export_data.xlsx
+++ b/data/export_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E460"/>
+  <dimension ref="A1:E750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11918,6 +11918,7256 @@
         <v>76</v>
       </c>
     </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7662626617000217876</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Pha giải cứu đi vào lòng đất khiến anh chồng chỉ biết đứng hình mất vài giây! 🤣</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuei #haihuoc #vochong #cuoixiu</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7654935686490901780</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Tưởng nhặt được tiền là đời sang trang, ai ngờ gặp ngay cái kết dở khóc dở cười!</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuuoi #haihuoc #cuoibebung #tinhhuonghai</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7668556023782837524</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Chỉ ngửi nhẹ một cái thôi mà biểu cảm như vừa ngộ ra "mùi đời", xem xong không cười không lấy tiền! 😂</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #dongvathai #haihuoc #cuoimoingay</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7682654205131115797</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Đúng là ảo thuật gia hệ liều, ghẹo gái xong không vắt chân lên cổ chạy nhanh là ăn đòn như chơi! 🤣💨</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuuoi #haihuoc #aothuat #cakhia</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7665956352983846164</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Đang yên đang lành tự nhiên gặp ca khó, chị nhà xử lý trong một nốt nhạc làm ai xem cũng phải bật cười! 🤣</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuei #haihuoc #videohai #giaitri</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7654084607582686485</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Đang hăng say mò cá thì gặp ngay pha "hú hồn" dưới nước khiến anh trai giật bắn người! 🤣</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuei #haihuoc #cuoithaga #haihuocmoingay</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7673752888254057748</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Tưởng đi tập gym để độ cơ, ai ngờ dính quả "úp sọt" bất ngờ khiến cả phòng đứng hình. Anh em xung quanh nhìn mà vừa thương vừa ghen tỵ! 🤣</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacui #haihuoc #gym #giaitri</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7667807467438443796</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Chỉ là đi mua xúc xích thôi mà làm gì dữ vậy ông anh? Mấy đường côn làm cả siêu thị đứng hình luôn! 🤣</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuuoi #haihuoc #giaitri #vothuat</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7658167450621758741</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Đang miệt mài sửa xe thì bị vợ thả "vị khách xanh" vào quần, pha bật dậy nhanh hơn chớp xem mà cười xỉu! 😂</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #troll #vochong</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7659282585268292885</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Đừng vội bênh vực ai, biết đâu cái kết lại khiến bạn phải cười xỉu vì sự công bằng này! 🤣</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #cuoixastress #nghiepquat</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7657349590433287445</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Đời tung bao nhiêu combo "cú lừa" cũng chịu thua với cái kết này, xem không cười không lấy tiền!</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacui #haihuoc #cuoiteghe #tinhhuonghai</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7655564457422245141</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Tưởng đàn ông bản lĩnh lắm, ai ngờ chỉ cần thử đúng một câu là "dính chấu" ngay! Chị em đã kiểm chứng chưa? 🤣</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacui #haihuoc #danong #haitan</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7651431537484778773</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Đang thiu thiu ngủ trưa mà gặp vị khách "không mời" này thì đố ai nằm yên được! Có bạn nào rơi vào tình huống hú vía như thế này chưa? 😂</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #cuoinganghieng #dongvattinhnghich</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7649578296014802196</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Vợ né pha hắt xì cực đỉnh nhưng vẫn không đỡ nổi nước đi siêu lầy của ông chồng! 🤣</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #trollvo #vochonghai</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7652212562351754516</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Màn "tranh chấp thời trang" gắt nhất phố hôm nay thuộc về chú chó này! Ai xem xong cũng phải bật cười nghiêng ngả. 😂</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #chotinhnghich #videohaihuoc</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7660750028926913812</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Nhìn điệu nhảy người ngoài hành tinh này xem có đỡ nổi không, tui là tui chịu thua rồi đó! 👽🤣</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuuoi #haihuoc #aliendance #giaitri</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7649577635508538644</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Cái kết dở khóc dở cười cho cô gái khi lỡ va phải sự tò mò của hội "danh hài" bốn chân! 😂</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #dongvathai #haihuoc #gietthoigian</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7648851988981075220</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Cái kết đắng cho sự tò mò, vừa ngửi thử một cái là chú bò xỉu ngang lăn đùng ra cỏ! 😂</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacoi #haihuoc #cuoixiu #dongvathaihuoc</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7647767710352346389</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Tò mò ngửi thử một cái mà làm như trúng độc, lăn đùng ra cỏ giãy đành đạch thế này! 😂</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #cuoixiu #dongvat</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7644431621004741909</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Nghe không hiểu một chữ nào mà cái sự hài hước này nó cuốn dã man, xem lại mấy lần vẫn cười muốn xỉu! 😂</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #videohai #haihuoc #giaitri</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7645263290972638484</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Đang phân tích vô cùng căng thẳng thì một câu nói xuất hiện làm ai cũng "xỉu ngang" vì buồn cười! 😂</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #cuoibebung #videohai</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7646263174647385364</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Nhìn qua tưởng món ngon khoái khẩu, nhìn kỹ lại mới biết cuộc đời cho ăn "cú lừa"! 😂</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuei #haihuoc #cuoixiu #culua</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7643264740961176852</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Sáng tạo thì có thừa nhưng cái kết lại khiến ai nấy cạn lời với hội bạn thân này! 🤣 Xem xong không cười không lấy tiền.</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #docla #cuoiteghe</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7642576629897710869</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Trao cho mấy bé dê sự dịu dàng, ai ngờ nhận lại cú húc "tình thương mến thương" đi vào lòng đất! 😂</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #dongvathaihuoc #bode</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7641072615074843924</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Tưởng là lãng tử ngầu đét, ai ngờ cái kết lại làm cả nhà bật ngửa!</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuei #haihuoc #cuoixiu #cliphai</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7638601831760842004</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Nhìn cái nết ăn là biết hài hước từ trong máu, coi tới ông cuối mà cười xỉu up xỉu down! 🤣</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacui #haihuoc #cuoixiu #videohai</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7636728796439121172</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Nụ cười bằng mười thang thuốc bổ, xem clip này xong bảo đảm bổ cả ngày luôn nha!</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuei #haihuoc #cuoibebung #giaitri</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7635454352253046037</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Tưởng phong lưu lãng tử thế nào, hóa ra coi tới cuối mới biết là "cây hài" chính hiệu!</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #cuoingaghien #langtu</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7637463432425393428</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Nhìn vừa thương vừa không nhặt được mồm, đúng kiểu đau một người mà cả xóm cùng vui! 🤣</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuei #haihuoc #fail #tenga</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7634856112583445780</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Màn phối hợp "đi vào lòng đất" đúng nghĩa đen của chủ và boss, coi xong chỉ biết cười nát nước mắt! 🤣</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #fail #thucung</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7634110082548206868</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Não vừa tắt nguồn 3 giây là có ngay pha xử lý cồng kềnh đi vào lòng đất! 🤣</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haivl #haihuoc #videohai</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7631785418366651668</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Quân tử thà chịu đau chứ nhất quyết không chịu nhục, tầm này là phải đứng lại combat khô máu luôn! 🤣</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #chodi #cuoixiu</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7631205879018179861</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Ủa meo, mày cũng đang thấy cái thứ vi diệu mà tao đang nhìn đúng không?</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuei #haihuoc #videohai #meme</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7629553131327655189</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Cái tội thích hóng hớt lại gần, ai ngờ nhận ngay cái kết "đắng ngắt"! 🤣</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacui #haihuoc #dongvat #fail</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7628470462208560405</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Nghịch dại cỡ nào mà cái kết lại trớ trêu kẹt luôn quả đầu thế này 🤣</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #fail #haivl</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7629330775061810453</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Tự nhiên thấy hình bóng hai vợ chồng nhà nào đó trong video này, đúng là "nóc nhà" lên tiếng thì ai cũng phải im lặng! 🤣</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuei #haihuoc #nocnha #videohai</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7627826817629555988</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Chỉ một giây lơ đễnh mà nhận về cái kết "đắng lòng" khiến ai xem cũng phải bật cười! 🤣</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuei #haihuoc #cuoibebung #fail</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7627121560574709012</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Tưởng không buồn cười mà buồn cười không tưởng với những pha xử lý "đi vào lòng đất" này! 🤣</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #cuoixiu #fail #haihuoc</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7626366150116396308</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Pha xử lý cồng kềnh thế này thì chỉ có nước xem xong cười xỉu thôi! 😂</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacui #haihuoc #fail #cuoisangkhoai</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7625995034852379925</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Ăn cay quá hóa dê luôn, vừa cất giọng một cái là nguyên đàn hưởng ứng hòa âm ngay! 🤣</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #ancay #cliphai</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7626745391786020116</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Xem tới đâu cười rớt hàm tới đó với mấy pha "xử lý đỉnh cao" này! 🤣</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuuoi #haihuoc #failhai #cuoisac</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7624712590245088532</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Nụ hôn "để đời" với chú tắc kè làm thanh niên khóc dở mếu dở, phải dùng chiêu độc mới thoát! 🤣</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haihuoc #tacke #videohai</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7625264856010181908</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Tỉa nhẹ cái trán thôi mà anh thợ lỡ tay đi hơi xa, xem xong chỉ biết cười nát ruột! 😭🤣</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacui #cattocfail #haivl #haihuoc</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7625631914594028821</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Thần may mắn gánh gãy lưng luôn, xem mà vừa thót tim vừa thấy buồn cười!</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #thottim #mayman #haihuoc</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7624153319493192981</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Tưởng làm dáng ngầu lòi lắm ai ngờ cái kết làm cả nhà cười xỉu! 😂</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacui #dongvat #haihuoc #cuoixiu</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7623397290048376084</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Đỉnh cao của sự kiên nhẫn: Gỡ không xong thì đập luôn cho nhanh gọn lẹ! 😭🔨</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacuoi #haivl #cuoisapmat #haihuoc</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7623791796274859284</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Định nhịn cười để tỏ ra lịch sự lắm rồi, mà cái nết nó không cho phép! 😂</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacui #haihuoc #cuoixiu #tainanhaihuoc</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lng.t2007/video/7622474672805891349</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Tưởng đi cắt tóc sương sương ai ngờ anh thợ ban cho quả kiệt tác độc lạ! 😳 Xem xong chỉ biết cười xỉu.</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>#ucircle #coilacutoi #haihuoc #tocdocla #barber</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Coi Là Cười</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7679787384967302421</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Mẫu bánh xe công trường cực ngầu dành riêng cho các bé mê cần cẩu, máy xúc đây ạ! Ba mẹ lưu lại ngay ý tưởng siêu đáng yêu này nhé 🚧❤️</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem #banhsinhnhatbetrai</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7673861258562571541</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>40 giây video lung linh là đổi bằng 40 phút nắn nót tỉ mẩn từng chút một đó cả nhà. Bánh tạo hình thủ công tuy tốn công nhưng thành quả thì đáng giá vô cùng!</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #lambanh #baking</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7683883061414513941</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Mấy cầu thủ nhí dạo này cứ mê tít mẫu bánh sinh nhật chủ đề bóng đá siêu đáng yêu này thôi! Các mẹ đã chọn được chiếc bánh ưng ý cho bé yêu nhà mình chưa nè?</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #banhsinhnhat #banhsinhnhatbetrai</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7681279123590958357</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Mẫu bánh sinh nhật Siêu Nhân Nhện cực ngầu dành riêng cho các hoàng tử nhỏ đây rồi! Ba mẹ lưu ngay gợi ý xinh xắn này về để tạo bất ngờ cho bé nhé 🍰🕷️</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem #spidermancake</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7684624630023310612</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Bánh vuông tạo hình Kuromi tone tím xinh hết nấc thế này thì team nghiện làm bánh sao cưỡng lại được! 🎀💜</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #kuromicake #maubanhsinhnhat</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7680171142086151445</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Mỗi ngày một mẫu bánh xinh cho hội mê ngọt đây! Mẫu bánh với thiết kế nhẹ nhàng siêu hot này đảm bảo xem xong là mê ngay. 🎀</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem #moubanhxinh</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7680805312575819029</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Mẫu bánh tàu vũ trụ siêu cưng dành riêng cho các phi hành gia nhí đây rồi! Các mẹ nhớ lưu ngay gợi ý này để làm quà bất ngờ cho bé nhé.</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem #maubanhxinh</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7686503340313726228</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Em heo hồng cưng xỉu thế này thì làm sao mà lỡ ăn đây cả nhà ơi! 🐽🎀</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkemtaohinh #banhsinhnhat</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7678674020870393109</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Chiếc bánh sinh nhật ngọt ngào thế này đã đủ làm tâm hồn mê bánh "đổ gục" chưa nhỉ? Mời cả nhà cùng ngắm nhìn thành phẩm siêu cưng hôm nay nhé!</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #maubanhsinhnhat #lovecakes</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7679055048235699476</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Mỗi ngày một mẫu bánh xinh: Gợi ý chiếc bánh tone xanh đơn giản mà cực kỳ tinh tế dành tặng cho bố 💙</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem #lambanh</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7676453207446506773</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Chiếc bánh kem tone "pink" siêu ngọt ngào và xịn xò ra lò rồi đây cả nhà ơi! 💗🎀</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #banhsinhnhat #lambanh</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7679420124180303124</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Mẫu bánh sinh nhật siêu cưng dành riêng cho các cầu thủ nhí mê bóng đá, ba mẹ lưu lại ngay nhé!</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem #maubanhsinhnhat</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7678559079014436116</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Sắp đến Trung Thu là máu "nghiện làm bánh" lại nổi lên, cùng em chuẩn bị phụ kiện trang trí bánh kem siêu xinh nha! ❤️✨</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkemtrungthu #trangtribanh #lambanh</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7675735910297701652</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Sinh nhật đôi nên làm hẳn hai chiếc bánh kem siêu cưng, mỗi người một cái khỏi lo tranh nhau nhé! 🎂✨</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem #lambanh</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7675330817060572436</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Đội "Nghiện Làm Bánh" đâu rồi, điểm danh xem ai lỡ bị đốn tim trước mấy bé gấu siêu cưng này nào! 🐻🎀</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #banhtaohinh #lambanh</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7674978431255268629</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Mẫu bánh bé heo dễ thương "quốc dân" lại ra lò đây, nhìn cưng thế này bảo sao các bé không mê cho được! 🐷✨</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem #lambanh</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7674294715684408597</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Chẳng cần cầu kỳ hoa mỹ, đơn giản thế này thôi cũng đủ làm hội mê bánh xiêu lòng rồi! 🍰✨</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #banhsinhnhat #lambanh</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7673115841357139220</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Vừa ngẫu hứng trang trí vừa làm chiếc bánh cho 2 anh em sinh đôi, thành quả xinh xắn thế này đã đủ đốn tim cả nhà chưa?</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #lambanh #gockhenhien</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7651543974234148117</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Mẫu bánh xinh xỉu thế này thì sao nỡ ăn đây các bác ơi! Chỗ mọi người một chiếc như này giá khoảng bao nhiêu nhỉ? 💗</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem #cakes</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7660860529119890708</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Chiếc bánh "em bé dưa hấu" xinh xắn đong đầy tình yêu thương của ba mẹ. Chúc em một đời bình an, mạnh khỏe và thật hạnh phúc nha! ❤️🍉</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem #lambanh</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7651186328989715732</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Chiếc bánh tone cam xinh xỉu thế này đã đủ làm các tín đồ mê bánh phải xiêu lòng chưa? 🍊✨</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #banhsinhnhat #lambanh</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7660102744631561493</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Sau bao ngày ở ẩn, hôm nay cùng em "tiền đình" bên những chiếc bánh kem ngọt ngào tiếp nhá! ❤️</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #banhsinhnhat #lambanh</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7647397514865315092</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Gợi ý mẫu bánh sinh nhật siêu đáng yêu cho các bé, các mẹ lưu lại tham khảo ngay nhé!</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7644907719337676052</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Mẫu bánh Hello Kitty xinh xỉu thế này thì bé nào nhìn cũng mê mẩn ngay thôi! 💗</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhhellokitty #banhsinhnhat #banhkem</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7644535566415039764</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Mẫu bánh siêu xinh theo yêu cầu đây nha cả nhà, nhìn thôi là đã muốn xắn tay vào bếp làm liền rồi!</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #lambanh #banhngot #cuocsongvaobep</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7643800820793838868</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Mẫu bánh ngọt ngào chiều lòng mọi phân khúc từ chồng yêu đến anh zai mưa, đảm bảo ai nhận cũng mê đắm! 🎂✨</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem #lambanh</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7639232110561168661</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Bỏ túi ngay mẹo làm bánh siêu đơn giản này để có chiếc bánh sinh nhật thật xinh nha! 💗</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #lambanh #handmade</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7644084051229363477</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Mỗi lần làm chiếc bánh tổng kết lại bồi hồi nhớ thời học sinh ghê, ước gì được quay lại cảm xúc háo hức chờ nghỉ hè ngày ấy!</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkemtongket #lambanh #lovecakes</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7636751482192235797</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Khách hối gấp cỡ nào thợ bánh nhà mình cũng "chiều" tới bến luôn nè! Nhìn thành phẩm xinh xắn thế này mệt mấy cũng thấy vui 🥰✨</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem #lambanh</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7640015694502956309</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Công thức làm bánh đơn giản trả lời theo yêu cầu của cả nhà đây nha! Cùng xắn tay áo vào bếp trổ tài ngay thôi nào.</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #lambanh #hoclambanh #congthuclambanh</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7641940879120403733</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Gắn phụ kiện lên bánh mà sợ khó lấy thì bỏ túi ngay mẹo siêu tiện này nhé các bà ơi! 🎂✨</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #meolambanh #banhkem #lambanh</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7636382098059709716</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Hạnh phúc của người làm bánh đôi khi chỉ đơn giản là được gửi trao bất ngờ trong ngày sinh nhật của ai đó. Nhìn mọi người rạng rỡ nhận bánh mà lòng mình cũng thấy ngọt ngào lây! ✨🎂</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #lambanh #lovecake</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7635627329821232405</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Một chiếc bánh đôi siêu ngọt ngào dành tặng cho bà và cháu gái đây ạ. Nhìn vừa xinh vừa ấm áp vô cùng! ❤️</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #lambanh #tiembanh</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7634072073194753301</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Đừng sợ cạnh tranh khi bắt đầu học làm bánh, cứ làm bằng cả cái tâm thì lộc tự nhiên sẽ đến thôi các bác ơi! ✨</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #hoclambanh #tiembanh</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7630684355869904149</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Khách mà đã mê thì thợ bánh cày xuyên đêm cũng thấy vui! Mọi người lưu ngay mẫu bánh ngọt ngào này lại để chiều lòng khách yêu nhé.</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #fondantcake #lambanh</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7627480772844244244</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Cuối tuần nhận đơn gấp em bánh Siêu nhân Nhện siêu ngầu, vội mấy thì vội nhìn thành phẩm vẫn mê xỉu luôn! ❤️</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #cakes #sieunhannhen</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7631951352788159765</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Nhìn xoay bánh một hồi muốn tiền đình luôn, nhưng thành quả xinh mê nấc thế này thì quá xứng đáng đúng không cả nhà? ❤️</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #maubanhsinhnhat #lambanh</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7620769268585516308</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Tone màu lịch lãm và tối giản dành riêng cho chiếc bánh sinh nhật của phái mạnh. Mọi người thấy mẫu trang trí này thế nào?</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #banhsinhnhat #trangtribanhkem</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7621920412082949396</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Cùng mình trang trí chiếc bánh sinh nhật siêu xịn tặng em trai với lời chúc tuổi mới sớm thành đại gia nhé!</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #lambanh #banhkem</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7619584748175805717</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Mẫu bánh kem xe cần cẩu siêu cưng dành riêng cho các hoàng tử nhỏ. Đảm bảo bé nào nhận được cũng thích mê!</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #banhkem #lambanh</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7618588073210793236</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Hôm nay vào bếp làm chiếc bánh kem xinh xắn ngọt ngào này cùng em nha các người đẹp ơi! 💗</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #banhsinhnhat #lambanh</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7613771200740756757</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Góc nhỏ thơm lừng mùi bơ sữa, nhìn thôi là đã muốn xắn tay vào bếp làm ngay một chiếc bánh xinh rồi!</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #lambanh #banhngot #hoclambanh</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7618137877897104661</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Vào bếp làm chiếc bánh kem ngọt ngào cùng mình nhé, nhìn thôi là đã thấy mê rồi! ❤️</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #banhsinhnhat #lambanh</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7590738878290578708</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Những chiếc bánh Hello Kitty đáng yêu thế này thì công chúa nhỏ nào mà không mê cơ chứ! 🩷✨</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #hellokitty #banhsinhnhat #lambanh</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7590780388843244821</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Bánh kem Kuromi tone tím vừa xinh vừa đáng yêu, đảm bảo bé gái nào nhìn cũng mê tít! 💜</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhkem #kuromicake #lambanh</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lovecakes_220/video/7591112103478447380</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Mẫu bánh Kuromi tone tím mộng mơ này chắc chắn sẽ làm các bé thích mê ngay từ cái nhìn đầu tiên! 💜</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>#ucircle #nghienlambanh #banhsinhnhat #kuromicake #banhkem</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Nghiện Làm Bánh</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7669853484065328392</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Góc setup mang phong cách Ghibli cực chill cho những ngày muốn thư giãn. Bạn có muốn sở hữu một không gian mộng mơ như thế này không?</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #ghibli #gamingsetup #pcsetup</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7628684824559062280</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Khi màn đêm buông xuống cũng là lúc góc chill này tỏa sáng. Bạn thấy tone xanh huyền ảo này thế nào?</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #gamingsetup #gocmaytinh</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7585999301180919058</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Góc setup tone xanh lá đỉnh cao thế này thì ngồi cày game cả ngày cũng không biết chán! 💚</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #gocmaydep #pcgaming</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7399306844394507528</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Góc máy tone trắng tối giản và ấm cúng thế này thì ngồi làm việc hay chơi game cả ngày cũng không chán.</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #whitesetup #pcgaming #desksetup</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7675406838531149074</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Biến phòng ngủ thành thiên đường gaming đỉnh cao thế này thì làm sao mà muốn ra ngoài nữa!</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #gamingroom #pcsetup</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7630869008182430984</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Siêu phẩm bàn phím Attack Shark R68 HE Carbon Fiber cực chất, nâng tầm đẳng cấp cho góc setup của bạn!</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #banphimco #gamingsetup #pcsetup</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7604546395139345671</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Góc nhỏ chill hết nấc thế này thì ở nhà cả ngày cũng không chán, tối nay ở lại đây cày game cùng mình nhé! 🩷</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcsetup #gocchill</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7668007890124426504</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Vừa nâng cấp nhẹ lại cái góc chiến game này, anh em chấm mấy điểm cho độ xịn xò này đây? 👀🔥</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcsetup #goclamviec</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7624208330906504455</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Sự kết hợp hoàn mỹ giữa sắc đỏ cá tính và trắng tinh tế cho góc máy cực chất. Bạn chấm phối màu này mấy điểm?</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcsetup #goclamviec</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7607526077413494023</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Góc làm việc chuẩn chỉnh thế này thì ngồi cày cả ngày cũng không biết chán! 🤍</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #gamingsetup #goclamviec</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7623071300797517074</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Siêu phẩm bàn phím Attack Shark R85 HE với độ nhạy Rapid Trigger cực đỉnh, mảnh ghép hoàn hảo cho góc setup của anh em!</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcsetup #banphimco</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7606047696998157586</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Trải nghiệm siêu mượt với em chuột AJAZZ AJ139P V3 sở hữu 24000 DPI cực chất. Nâng cấp ngay cho góc setup gaming của bạn thôi nào!</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #chuotgaming #pcsetup</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7601960486132829447</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Tháng 2 gõ cửa, cùng làm mới góc nhỏ để nạp trọn năng lượng chiến game và làm việc thôi nào! 💛</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #gamingsetup #goclamviec</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7600094969075862792</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Góc chill lý tưởng để nạp lại năng lượng sau một ngày dài. Anh em chấm góc máy này mấy điểm?</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcsetup #gocmaydep</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7598241804105862407</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Góc máy tone trắng đậm chất 2B cực phẩm thế này đã đủ làm bạn mê mẩn chưa?</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcsetup #desksetup</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7598982646231944466</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Chào mừng em "baby" Attackshark X68 PRO HE gia nhập góc setup, nhìn vừa ngầu vừa xịn thế này sao cưỡng lại được!</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #banphimco #pcsetup</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7597126575460519176</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Nhìn góc setup xịn xò thế này thì cày game cả ngày cũng không biết chán, anh em chấm mấy điểm?</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcsetup #gocmaydep</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7590446444633394450</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Góc nhỏ đón năm mới siêu chill thế này thì làm việc hay cày game cả ngày cũng chẳng muốn rời!</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcsetup #gocmaydep</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7595262404682960136</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Góc máy đậm chất Jinx thế này thì làm sao mà cưỡng lại được, anh em chấm mấy điểm cho setup này?</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcsetup #gaming</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7588595718231837959</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Góc làm việc chất như thế này thì bảo sao dính ghế cả ngày không muốn rời. 💙</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcsetup #goclamviec</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7593785043911183623</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Chọn một dàn PC xịn đét để chiến game hay túi Chanel sang chảnh đây các bác?</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #gamingsetup #gocmaytinh</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7592658302136339720</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Binh đoàn vịt vàng "xâm chiếm" góc setup siêu cute! Ngắm thế này thì làm sao mà tập trung làm việc đây?</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #gamingsetup #desksetup</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7589338052342844680</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Nhìn lại hành trình hoàn thiện góc nhỏ đam mê trong năm qua, cảm ơn mọi người đã luôn đồng hành và ủng hộ!</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcsetup #goclamviec</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7591556644665003282</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Sao phải nghiêm túc thế nhỉ? Cứ bật góc máy cực chất này lên là mọi căng thẳng tan biến ngay!</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #gamingsetup #gocmaydep</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7587481178014338322</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Tầm này thì phải gọi tôi là vua của các góc setup nhé! 👑</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcsetup #gocmaydep</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7585257933018008850</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Muốn sở hữu một góc làm việc tối giản và tinh tế thì không thể bỏ qua ý tưởng setup này!</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #setupgocmay #gamingsetup</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7583779578796182792</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Góc máy vừa xinh vừa xịn thế này thì ngồi cày game cả ngày cũng không thấy chán! 😸🤍</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #custompc #gocmaydep</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7579985666637942034</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Chỉ muốn chạy ngay về nhà để đắm mình vào góc setup vừa xịn vừa chill này thôi! ❤️🤍</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcgaming #goclamviec</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7574051782704237832</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Góc setup tone xanh cool ngầu thế này thì chiến game cả ngày không chán! Anh em chấm góc này mấy điểm?</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #gaming #desksetup</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7581185610518383890</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Khi màn đêm buông xuống cũng là lúc góc chill sắc tím này tỏa sáng. Bạn chấm mấy điểm cho góc setup đắm đuối này?</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #custompc #desksetup</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7571512054570372360</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Góc setup cực mê lấy cảm hứng từ Hà Trụ Muichiro Tokito với tone xanh dịu mát. Bạn đánh giá mấy điểm cho không gian này?</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #desksetup #gamingpc</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7582662643316657415</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Show nhẹ bộ cấu hình PC cực chiến cho anh em tham khảo. Anh em chấm mấy điểm cho dàn máy này?</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcgaming #gamingsetup #custompc</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7531448733528001799</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Góc máy tông trắng tối thượng lấy cảm hứng từ thầy Gojo, nhìn thôi là đã thấy tràn ngập năng lượng chiến game!</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #gojo #gamingpc</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7530330765129780488</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Nhẹ nhàng nâng cấp góc máy với một em PC tông trắng siêu thanh lịch. Đẹp thế này thì ngồi làm việc hay cày game cả ngày cũng không chán!</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #desksetup #pcgaming #minimalsetup</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7479852514284670216</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Góc máy tone vàng cực "cháy" lấy cảm hứng từ Monster Hunter Wilds! Anh em đã sẵn sàng săn quái vật cùng góc setup siêu phẩm này chưa?</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #monsterhunter #pcgaming</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7471641986710260999</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Góc setup tone trắng xanh mát lạnh như tuyết thế này thì anh em có muốn ngồi luyện game cả ngày không?</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #pcgaming #desksetup</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7444591305423850770</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Biến góc máy thành không gian bình yên đậm chất thiên nhiên lấy cảm hứng từ Frieren. Ngồi vào đây là mọi mệt mỏi đều tan biến!</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #setupgocmay #frieren</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7460222072371924232</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Tone màu tím huyền bí luôn là chân lý giúp góc máy trở nên mê hoặc hơn bao giờ hết. Bạn thích phối màu nào cho góc setup của mình?</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #desksetup #gaming</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7440834427267173639</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Vừa F5 lại góc máy cực chất này, anh em chấm mấy điểm? Comment ngay nếu muốn tớ làm giveaway em lót chuột siêu ngầu này nhé!</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #gocmaydep #gaminggear</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E593" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7424933743204289810</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Góc máy cực chill với sự kết hợp huyền ảo giữa sắc xanh cyan và hồng neon nổi bật. Đêm xuống chỉ cần bật đèn lên là chuẩn gu ngay!</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #neonlights #gaming</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7430835434067938567</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Góc máy tone xanh Joker cực ngầu thế này thì cày game cả đêm cũng không biết mệt. Anh em chấm mấy điểm cho góc setup này?</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #gamingpc #gocmaydep</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7420808458045345031</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Góc máy tone đỏ - trắng đậm chất Itachi cực ngầu cho anh em đam mê PC. Bạn chấm mấy điểm cho góc setup đỉnh cao này?</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #gaming #itachi</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E596" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7409709413625285896</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Lên đồ cho góc PC thế này đã đủ khiến anh em mê mẩn chưa? Cho mình xin ít đánh giá bên dưới nhé!</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcsetup #gocmaydep #pcgaming</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E597" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7402261445469097224</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Chuẩn bị trình làng bộ PC mới cực phẩm, anh em đoán xem cấu hình lần này khủng cỡ nào nhé!</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcgaming #setupgocmay #gamingsetup</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E598" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7407465458187635986</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Biến góc máy thành "Lãnh Địa Vô Hạn" với tone xanh trắng cực chất lấy cảm hứng từ Gojo Satoru!</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcgaming #gojo #setupgaming</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E599" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7397068527980580114</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Tone tím mộng mơ vừa dịu mắt vừa chill hết nấc cho những buổi cày game đêm. Anh em chấm mấy điểm cho góc setup này?</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #gamingsetup #pcgaming #setup</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E600" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7392292141935971602</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Ánh mắt đầy thần thái này đang nhắm tới mục tiêu nào đây? Nhìn góc setup đỉnh thế này thì thức đêm cày game cũng đáng!</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #pcgaming #demonslayer #setupdecor</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E601" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@iitachi.pc/video/7390059360057068818</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Góc setup của bạn đang mang tone màu chủ đạo nào? Khoe ngay góc máy xịn xò của bạn bên dưới cho mọi người cùng ngắm nhé!</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>#ucircle #gocsetup #setupgocmay #pcgaming #desksetup</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Góc Setup</t>
+        </is>
+      </c>
+      <c r="E602" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tu_rophi/video/7684587499867393300</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Kiên trì săn rô phi mâm mấy năm liền, đến mùa 2026 thì lại nhận kết đắng. Có anh em cần thủ nào mùa này cũng đang chịu cảnh "móm" giống tôi không?</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caucatunhien #caucagiaitri #cauca</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E603" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tu_rophi/video/7252940693763607813</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Lại thêm 2 em rô phi tự nhiên "hàng khủng" từ anh em cần thủ Gia Lai, nhìn là mỏi tay giật cần liền!</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caucatunhien #caucagiaitri #canthu</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E604" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7589819745747258631</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Nạp chút vitamin ngọt ngào cho ngày mới tràn đầy năng lượng nào!</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #hotgirl</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E605" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7578325540659137799</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Nạp chút "vitamin ngọt ngào" này cho ngày mới của bạn luôn rạng rỡ nha!</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #dance</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E606" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7582140805574348040</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Liều vitamin xinh đẹp này đủ để làm bừng sáng ngày mới của bạn chưa?</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E607" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7590955327881858311</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Gửi chút "vitamin xinh đẹp" cho ngày mới rực rỡ, nhìn một lần là say cả đời đấy nhé! ✨</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #hotgirl</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E608" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7590613648762998034</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Nạp chút vitamin xinh đẹp để ngày mới của bạn luôn ngập tràn năng lượng tích cực nhé!</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #gaidep #xinhdep</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E609" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7591869706974317842</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Gửi chút "vitamin ngọt ngào" cho ngày mới của bạn thêm tràn đầy năng lượng nè!</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E610" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7590340700584135954</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Nạp chút vitamin ngọt ngào cho ngày mới tràn đầy năng lượng nhé!</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E611" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7584773074633919751</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Nạp chút "vitamin gái xinh" cho ngày mới tràn đầy năng lượng và vui vẻ nhé!</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #viral</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E612" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7587613222316887314</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Một chút "vitamin xinh đẹp" nạp đầy năng lượng cho cả ngày dài của bạn đây! ✨</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #viral</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E613" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7588334706463116551</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Gửi tặng bạn chút "vitamin ngọt ngào" cho ngày mới tràn đầy năng lượng tích cực nhé!</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E614" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7588837586429431058</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Gửi chút "vitamin xinh đẹp" cho ngày mới của bạn thêm rạng rỡ nè! ✨</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #trending</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E615" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7587348398240468232</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Thả chút "vitamin ngọt ngào" cho ngày mới của bạn thêm rạng rỡ nè!</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xuhuong #xinhdep</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E616" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7585926724861365522</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Nạp chút "vitamin xinh đẹp" cho ngày mới rực rỡ hơn nè!</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #beauty</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E617" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7586240838016011528</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Gửi tặng bạn chút "vitamin ngọt ngào" cho ngày mới tràn đầy năng lượng nè!</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #gaiyeu</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E618" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7586918285170560264</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Nạp chút "vitamin xinh đẹp" cho ngày mới tràn đầy năng lượng nhé cả nhà!</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E619" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7585575571971755282</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Chút vitamin ngọt ngào cho ngày mới tràn đầy năng lượng, nhìn thôi là đủ thấy xiêu lòng rồi!</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E620" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7584600935926713607</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Nạp ngay một chút "vitamin xinh đẹp" cho ngày mới tràn đầy năng lượng thôi nào!</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #gaintuoi</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E621" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7585049778182966546</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Nụ cười rạng rỡ này có đủ làm bạn "tan chảy" chưa? Gửi chút vitamin ngọt ngào cho ngày mới nhé!</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E622" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7584978730666216711</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Nạp chút vitamin xinh đẹp này để cả ngày tràn đầy năng lượng tươi mới nhé! ✨</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E623" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7584307231940742418</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Gửi tặng bạn chút vitamin xinh đẹp cho ngày mới luôn tràn đầy năng lượng nhé!</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #hotgirl</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E624" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7584246678866136328</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Nạp chút vitamin xinh đẹp cho ngày mới tràn đầy năng lượng nha!</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #hotgirl</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E625" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7585366453398834450</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Nạp ngay một chút "vitamin xinh đẹp" cho ngày mới tràn đầy năng lượng nhé!</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E626" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7583942067508776200</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Nụ cười này có đủ làm ai đó xiêu lòng chưa nhỉ? Thêm chút "vitamin xinh đẹp" cho ngày mới tràn đầy năng lượng nha!</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E627" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7583866429661924626</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Nạp chút vitamin ngọt ngào cho ngày mới tràn đầy năng lượng nào. Nụ cười này đã đủ làm ai đó xiêu lòng chưa?</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E628" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7583126753648921863</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Trông xinh xắn thế này thôi chứ hay suy lắm, ai dỗ dành là đổ liền đó nha!</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #haysuy</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E629" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7583503529717894407</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Nạp chút vitamin xinh đẹp cho ngày mới tràn đầy năng lượng nào! Nụ cười này có đủ làm ai đó xiêu lòng chưa nhỉ?</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E630" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7583285277603548423</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Nạp chút "vitamin xinh đẹp" cho ngày mới rực rỡ nè, tim đâu hết rồi nhỉ?</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E631" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7583645350343314706</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Con gái Việt Nam luôn sở hữu nét cuốn hút rất riêng, ngắm hoài mà không biết chán! 🇻🇳✨</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #girlvietnam #vitamingirl #xinhdep</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E632" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7582894846390701319</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Gửi chút "vitamin xinh đẹp" cho ngày mới tràn đầy năng lượng nha! ✨</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xuhuong</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E633" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7582952589461933330</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Nụ cười ngọt ngào thế này đã đủ làm ai đó xao xuyến cả ngày chưa?</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #anhbo #xuhuong</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E634" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7582744140744543495</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Nạp chút vitamin ngọt ngào cho ngày mới thêm rực rỡ nè, nhìn thế này đã đủ làm ai đó xiêu lòng chưa?</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xuhuong #gaidep</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E635" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7582924218019400968</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Nạp ngay một chút vitamin xinh đẹp để ngày mới tràn đầy năng lượng nhé!</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E636" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7582609033031355666</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Nụ cười này chính là liều vitamin ngọt ngào tiếp thêm năng lượng cho ngày mới của bạn đấy!</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xuhuong</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E637" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7582219227998850311</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Nhạc cuốn một thì visual này phải cuốn mười, lướt qua thấy xinh nhớ thả tim cho em nha!</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E638" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7582378670942178578</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Người ta gọi em là Yêu, nhưng thật ra tên đầy đủ của em là Yêu Anh đấy nha.</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E639" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7582180288634096904</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Nạp chút vitamin ngọt ngào cho ngày mới luôn rạng rỡ và tràn đầy năng lượng nào!</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xuhuong #xinhdep</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E640" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7582537388501634311</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Xinh thế này mà cứ hay suy, có ai muốn đến làm người dỗ dành em không?</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #gaixinhhaysuy</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E641" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7582466010511396114</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Nạp chút vitamin xinh đẹp cho ngày mới tràn đầy năng lượng nào! ✨</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #gai_dep</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E642" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7582164767331110151</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Chút "vitamin ngọt ngào" cho ngày mới tràn đầy năng lượng đây nè!</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #embem72 #xinhdep</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E643" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7582199850096282898</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Nạp chút "vitamin xinh đẹp" cho ngày mới thêm rạng rỡ và tràn đầy năng lượng nào! ✨</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #gocxinh</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E644" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7581787810844265746</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Một chút "vitamin xinh đẹp" tiếp thêm năng lượng tràn đầy cho cả ngày dài của bạn nè!</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xuhuong</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E645" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7581755618378190087</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Một liều vitamin xinh đẹp để sạc lại năng lượng cho cả ngày dài. Liệu đã đủ làm ai đó xiêu lòng chưa nhỉ?</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #gaidep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E646" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7581711299525102866</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Nạp chút "vitamin xinh đẹp" cho ngày mới tràn đầy năng lượng cùng mình nhé!</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #gaixinhvietnam</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E647" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7581688291754265874</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Nhìn khẽ một giây thôi mà lỡ làm đốn tim biết bao nhiêu người rồi đấy.</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #xinhdep #xuhuong #lanxinhyeu</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E648" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7581629623893576967</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Nạp chút "vitamin xinh đẹp" cho ngày mới thêm rạng rỡ nè!</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E649" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7581336178331307271</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Nạp ngay một chút "vitamin xinh đẹp" để ngày mới luôn tràn ngập năng lượng tích cực nhé!</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xuhuong #xinhdep</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E650" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7580985134220971272</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Nụ cười tỏa nắng này có đủ làm ai đó "tan chảy" chưa nhỉ?</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E651" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7580915384082025736</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Nạp chút "vitamin xinh xắn" cho cả ngày tràn đầy năng lượng nào!</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E652" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7581520372445580552</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Nạp chút "vitamin ngọt ngào" này cho ngày mới tràn đầy năng lượng nhé!</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #ngotngao</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E653" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ngaytiziat5/video/7581667224096640274</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Nạp chút "vitamin xinh đẹp" cho ngày mới tràn đầy năng lượng và ngọt ngào nào! ✨</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>#ucircle #gaixinh #vitamingirl #xinhdep #xuhuong</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Gái Xinh</t>
+        </is>
+      </c>
+      <c r="E654" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7686823969604898055</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Lại tiếp tục báo cá khủng nha anh em, kéo em Hugo này đúng phê ê cả tay! Cần thủ nhà mình hôm nay đã lên hàng chưa?</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #hugo #cauca</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E655" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7574668255546084615</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Cuối tuần xả stress cùng đam mê câu lure, anh em cần thủ hôm nay thu hoạch thế nào rồi?</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #cauca #caulure #fishing</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E656" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7670773928104561938</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Cuối tuần xách cần đi lure nhẹ nhàng mà dính ngay hàng khủng, đúng là niềm vui khó tả của anh em cần thủ!</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #fishing</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E657" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7576149808365292807</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Lũ tan nước lại trong rồi, anh em cần thủ lên đồ vác cần ra khơi săn hàng thôi nào!</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #cauca #caulure #canthu</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E658" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7677454484494109959</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Đi câu mà gặp quả pha "dở khóc dở cười" này thì đỡ làm sao nổi anh em nhỉ? 🤣</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #canthu #fishing</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E659" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7547228770151730440</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Ráng quăng thêm một đường lure nữa là cá cắn câu ngay! Đam mê này đúng là khó dứt quá anh em ơi. 🎣🐟</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #cauca #caulure #canthu</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E660" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7686448073400175879</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Con cá lũ đầu mùa kéo dính tay quá các bác ơi, mở bát năm nay xem chừng rực rỡ rồi!</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #canthu</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E661" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7683761640596180231</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Bảo do kỹ năng thì lại bảo nổ, thôi thì cứ nhận hôm nay đi câu may mắn vậy các bác ạ!</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #canthu #cauca</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E662" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7669290352716598546</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Kéo rát cả tay mới đưa được em cá khủng này lên bờ, cảm giác phê không tưởng luôn anh em ơi!</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #fishing</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E663" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7660759382468168968</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Đam mê câu lure là phải kiên trì, chỉ cần một cú táp bọt tung trời là đủ sướng cả ngày!</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #fishing #dammecauca</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E664" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7658492381376810258</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Cứ nhấp nhấp nhẹ tay là cá đớp mồi ngay, cảm giác kéo cần nó đã gì đâu anh em ơi!</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E665" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7663718551986900231</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Pha đóng cá căng đét thế này thì chỉ có anh em cần thủ mới hiểu hết cảm giác phấn khích!</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #fishing #dammecauca</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E666" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7667823737680432392</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Lâu lắm mới tìm lại được cảm giác đóng hàng Hugo sướng rần tay! Em này tầm 5, 6 lạng đã đủ chuẩn trùm Tân Phước chưa anh em cần thủ?</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #hugo #cauca</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E667" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7655190297932025096</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Cú đóng cá quá chất lượng, nó phi thân nhảy tưng tưng phê gì đâu anh em ơi!</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #canthu</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E668" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7670402322605870343</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Thèm cái cảm giác giật cần và tiếng máy câu reo lên cực đã anh em ơi! Hôm nay anh em đi lure có săn được con hàng chất lượng nào không?</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #fishing</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E669" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7657030108225506578</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Tầm 6h chiều xách cần đi chill, đúng khung giờ vàng thả lure của anh em cần thủ!</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #canthu #fishing</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7654077201452911879</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Cuối tuần xách cần lên và đi thôi anh em ơi, hôm nay ai có chiến tích gì thì khoe ngay cho Hội rửa mắt nào!</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #canthu</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7652964834950090002</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Nhìn cú táp mồi mượt thế này thì cá nào chịu cho nổi, anh em cần thủ đã lên đồ đi săn chưa?</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #canthu #fishing</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7650737773250383122</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Cảm giác cú đớp mồi đóng cá nổ chát luôn là lý do khiến anh em cần thủ mê mẩn món lure này.</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #fishing</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7649257731995585810</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Tân Phước dạo này cá chê mồi quá các bác ơi, có điểm lure nào êm hơn chỉ em với!</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #catanphuoc</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7651121414484806930</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Trời đang mưa lâm râm mà cá táp một phát rầm giật cả mình, tưởng sét đánh tới nơi chứ anh em! 😂</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #canthu</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7646285309839265042</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Cuối tuần gác lại mọi lo toan, làm quả lure bén như thế này thì còn gì bằng anh em ơi!</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #fishing #caucavietnam</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7644434148085533970</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Cứ đến sát bờ cá mới chịu táp làm giật cả mình, đóng cần toàn hụt! Có anh em nào đồng cảnh ngộ không?</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #fishing #cauca</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7647769108859129096</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Một nhịp kéo dính liền hai em cá thì cảm giác nó lại quá là êm luôn anh em ơi! 😁</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #fishing</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E678" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7641835193891835144</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Đóng cá phát một cực đã tay, anh em cần thủ hôm nay đã được giật cần chưa?</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #fishing #canthu</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7643696125794389256</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Cuối tuần không đi câu được thì ghé đây xem mình giật cá cho đỡ ghiền nha anh em! 🎣🔥</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #dammecauca</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7638117456388574472</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Nhìn đường lure mượt mà thế này thì cần thủ nào mà chịu cho nổi! Anh em hôm nay đã ra hồ làm vài đường chưa?</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #canthu</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E681" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7635894262059568391</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Pha đóng cá cực phê thế này thì chỉ có cần thủ mới hiểu. Cuối tuần rồi, lên đồ đi săn cá khủng thôi anh em ơi!</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #fishing</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E682" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7622548164633136392</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Test nhẹ em nhại hơi dưa hấu là có cá ngay, đúng là hàng bén cho anh em cần thủ!</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #nhaihoi</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E683" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7630271365844585736</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Lâu lắm mới lại lên clip đi lùa cá, các bác cần thủ vào giao lưu cho xôm nhà xôm cửa nhé!</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #fishing</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7631726642037017874</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Ngồi canh mỏi mắt thì cá chẳng thèm ngó, vừa ngoảnh mặt đi một cái là nó táp liền! Đúng là quy luật bất biến của dân mê câu.</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #meccauca</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7619937796274392328</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Nhái hơi dưa hấu đúng là "sát cá", chỉ cần quăng dây kéo nhẹ một đường là dính hàng ngay! 😁</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #nhaihoi #cauca</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7598785186561543431</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Mai có anh em cần thủ nào lên kèo Tân Phước không, lập hội đi chung cho xôm nhỉ?</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #fishing #tanphuoc</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7614743699506908424</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Cứ thấy tăm cá là giật lụm liền, cảm giác đè cần sướng không gì tả nổi!</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #fishing #cauca</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7609181003910745352</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Cảm giác giật cần cực căng và tiếng máy reo luôn là liều thuốc chữa lành tuyệt vời nhất. Anh em hôm nay đi câu có "lên hàng" không?</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #canthu</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7593595779986787591</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Gửi anh em bãi câu ruột "chống móm" siêu uy tín, cứ buông cần là chắc chắn có cá!</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #canthu</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7595819244248370439</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Đánh nhái thật cả buổi cá không thèm ngó, đổi sang nhái hơi vài đường là lụm ngay em hàng cực chất! 🎣🐟</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #nhaihoi #cauca</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7610288219631979794</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Khai cần mùng 7 Tết va ngay em Hugo Tân Phước quá êm anh em ơi!</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #hugotanphuoc</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7588767152837119239</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Vừa ngoi lên thở thì mồi rơi tọt vào họng luôn, câu cá nhàn thế này thì chịu rồi anh em ạ! 😂🎣</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #fishing</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7591365564522679570</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Cái cảm giác dây căng cần cong nó tê tê phê phê gì đâu anh em ơi!</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #fishing</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7583943834866846994</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Kiên trì chèo qua 80 líp khóm ở Tân Phước mới "dụ" được một em cá về tay. Bộ môn này đúng là vừa hành xác vừa gây nghiện mà các bác! 😂</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #caulure #cauca #canthu</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7570964366254673159</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Cá lũ ăn mạnh thế này thì dùng mồi H1 Tiểu Long Nhi đúng là "bài tẩu" luôn anh em ơi! 🎣🐟</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #cauca #caulure #fishing</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7573567267305295122</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Chủ nhật làm vài cú lure dính cá dồn dập thế này thì còn gì êm bằng! Anh em cần thủ cuối tuần có "bội thu" không nào?</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #cauca #caulure #fishing</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7570578875508329746</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Hôm qua móm mỏ chứ hôm nay thì chưa chắc đâu nha các cần thủ! 😁</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #cauca #caulure #canthu</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7573141945489378578</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Sau 4 ngày "móm" mỏ, giây phút cần cong vút này đúng là mừng hơn trúng số các cần thủ ơi! 😁</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #cauca #caulure #canthu</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7569470465622805768</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Cá bạ Hòa Khánh Tây đang chịu ăn mạnh lắm nha, anh em cần thủ tranh thủ xách cần lên đường ngay thôi! 🐟🎣</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #cauca #caulure #canthu</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7565392510000893202</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Chiều mát vác cần ra hồ chill nhẹ, thế thôi mà mê không lối thoát! 🎣</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #cauca #caulure #fishing</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7562422372284910866</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Kéo nhẹ nhàng tình cảm thế thôi mà dính hàng ngay! Anh em hôm nay đi săn được em nào chưa?</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #cauca #caulure #fishing</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7556861435733724434</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Cần thủ làm gì có ai nói dối, chỉ là con cá trong ký ức lúc nào cũng to hơn thực tế thôi! Khoe ngay chiến tích "khủng" nhất của anh em vào đây nào.</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #cauca #canthu #caulure</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@23thg0303/video/7556485573968530696</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Show ngay combo đi câu chất lượng nhất của anh em dưới phần bình luận cho cả hội chiêm ngưỡng nào! 🐟🎣</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>#ucircle #hoimecauca #cauca #caulure #fishing</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Hội Mê Câu Cá</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7690073186007928085</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Thua một trận thì đã sao, làm lại ván mới gánh team khét hơn ngay!</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gamethu #gameplay</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7661128951129050389</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Trang phục Nhất Tố bí ẩn vừa trình làng, anh em game thủ thấy siêu phẩm này có đủ sức làm anh em "chốt đơn" ngay không?</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gaming #gameff</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7689780896798346517</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Định "bật" mode thần sầu gánh team hay gì mà gáy căng thế bro, vào trận biết tay nhau ngay!</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #gamervn</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7687897278446701845</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Chưa kịp thể hiện gì mà đã "bay giải" trong một nốt nhạc, cay thật sự! Anh em có bao giờ gặp cảnh này chưa?</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #highlights</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7689794258219388180</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Gánh team là sứ mệnh, highlight là đam mê! Anh em chấm cho pha xử lý này mấy điểm?</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #game #highlight</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7688597154612464916</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Thua keo này mình bày keo khác, anh em vào kéo lại rank giúp tôi với nào!</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gamethu #xh</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7689684979844009237</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Pha gánh team cực khét thế này thì đối thủ chỉ có đứng hình thôi! Anh em chấm pha xử lý này mấy điểm nào?</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #highlightfreefire</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7681243978116779285</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Pha xử lý căng đét gánh team phút chót, anh em chấm mấy điểm cho màn lội ngược dòng này?</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gamethu #gaming</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E712" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7671833576396147988</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Thất bại chỉ là nháp, trận sau mới thể hiện đẳng cấp! Anh em leo rank hôm nay thế nào rồi?</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #leorank</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E713" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7664815310960151829</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Pha xử lý gánh tem mượt mà thế này, anh em nào đủ trình vào thách đấu với Cường không?</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #highlights</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7673707171103640853</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Tay run cầm cập luôn anh em ơi, tí nữa thì bay màu!</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gaming #highlightsgame</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7674477456748858644</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Thua trận này thì mình làm lại trận khác, game thủ chân chính làm gì biết bỏ cuộc!</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gamethu #cuocsonggamethu</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E716" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7664176894014688532</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Trận đấu căng thẳng nhất lịch sử với màn lật kèo không tưởng! Anh em chấm mấy điểm cho pha xử lý này?</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #gamelatkeo</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E717" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7664446374636801301</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Nhân tố bí ẩn K17 xuất hiện ẵm luôn giải đấu, đúng là cao thủ ẩn danh của làng Free Fire!</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gamethu #esports</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E718" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7664822407001132309</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Mấy em khối nghỉ hè dạo này bắn gắt thật sự, anh em leo rank có thấy rén không?</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #giatri</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E719" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7663758357320224021</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Pha kéo tâm chuẩn đét thế này đã đủ làm anh em mãn nhãn chưa?</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #highlight #gamethu</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E720" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7663681393012083989</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Tạm thua ván này để lấy đà gánh team ván sau thôi nhé anh em!</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #gamerviet</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E721" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7662603590489476373</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Đã vào trận là chỉ có chiến, từ "sợ" chưa bao giờ có trong từ điển nhé!</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #highlightgame #gamethu</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E722" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7661869403444677908</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Pha xử lý xuất thần thế này thì đúng là OMG luôn anh em ạ, cho ngay 10 điểm không có nhưng!</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #highlight #gameplay</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E723" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7661269077695991061</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Pha gank căng đét khiến đối thủ chỉ biết ngậm ngùi rời cuộc chơi! Anh em chấm mấy điểm cho pha xử lý này?</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #highlightgame</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7663343698888969492</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Chưa kịp gánh team thì đã bay giải trong một nốt nhạc! Anh em gamer có ai từng rơi vào cảnh này chưa?</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #gamervn</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7660491100636925205</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Pha giao tranh sinh tử quyết định cả ván đấu, liệu tui có lật kèo thành công không anh em?</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #highlightfreefire #gamethu</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E726" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7660039266050903317</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Thất bại là mẹ thành công, nhưng ngã đau thế này thì cay thật sự! Anh em vào kéo rank làm lại ván mới nào.</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>#cuongmegame #ucircle #freefire #gamethu #highlightsff</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E727" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7659672215209643285</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Pha xử lý đỉnh cao khiến đối thủ phải "bay giải" trong một nốt nhạc! Anh em chấm mấy điểm cho kỹ năng này?</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #highlightgaming</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E728" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7659351138847706389</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Thua chỉ là tạm thời, đẳng cấp mới là mãi mãi! Anh em kéo vào làm ván mới gỡ lại nào.</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gamethu #highlight</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E729" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7662144710156373268</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Coi giải đấu mà tưởng đang xem kịch hài, đúng là đỉnh cao bất ổn trên sóng livestream luôn anh em ạ!</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #highlight #gamenoi</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E730" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7659267597250088212</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Pha giao tranh quyết định vận mệnh cả trận đấu, anh em đoán xem liệu tớ có lật kèo thành công không nhé!</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #highlightgame #gameplay</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E731" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7655231302920178964</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Chưa kịp bấm sấy phát nào mà tay đã run lẩy bẩy, pha này áp lực thật sự!</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #gamethu</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E732" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7658847230761192725</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Thua một trận chưa nói lên điều gì, ván sau tui lại gánh cả team cho xem!</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gaming #gamehay</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E733" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7653683929727175957</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Pha xuất thần làm đứng hình mất 5 giây, anh em xem thấy có ảo diệu không nào?</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #highlightgame #gamethu</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E734" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7653072049346333973</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Giải đấu Free Fire trực tiếp cực căng đang diễn ra, anh em đã sẵn sàng vào xem và "cháy" hết mình chưa?</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #livestream #gameplay</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E735" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7652288935221038356</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Nhân tố bí ẩn xuất hiện gánh team cực khét, anh em xem xong có nhận ra cao thủ này là ai không?</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #garenafreefire #gamemobile</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E736" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7651543995096616213</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Lên đồ vào bo chiến ngay thôi anh em ơi, hôm nay quyết tâm gánh team lấy top 1!</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gaming #top1</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E737" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7652960458546187541</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Pha giao tranh gánh team căng đét luôn anh em ơi, xem mà nín thở!</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #highlights</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E738" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7650433734457494805</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Tưởng gánh team cực ngầu, ai ngờ pha xử lý này lại khiến cả team bay giải luôn!</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #haigame</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E739" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7647444870268734740</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Chuỗi thắng thứ 659 chính thức được thiết lập, liệu có cao thủ nào đủ sức cản bước đây?</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gamethu #gameplay</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E740" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7648567906141293844</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Giải đấu Free Fire cực nảy lửa đang được phát trực tiếp trên Live đây anh em ơi! Liệu ai sẽ bước lên ngôi vô địch ngày hôm nay?</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #livestreamgame #gameplay</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E741" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7647089051882867988</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Chuỗi thắng thứ 650 rồi đấy, có ai đủ trình vào cản bước Cường không nhỉ?</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #chuoithang #gamethu</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E742" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7642649282528529685</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Đang thi đấu giải cực cháy trên Live mà bị "bay màu" ngay lập tức thì cay cỡ nào anh em?</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #highlights #gaming</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E743" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7639306982427594004</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Đang đấu giải căng thẳng mà bị "bay màu" trực tiếp trên livestream thì biết giấu mặt đi đâu anh em ơi!</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gamethu #livestream</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E744" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7638576053652426004</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Trận đấu sinh tử căng như dây đàn, sơ hở một giây là bay luôn khỏi giải đấu! Anh em xem liệu tớ có lật kèo thành công không nhé?</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #esports #gameplay</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E745" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7638935835764690197</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Đang thi đấu giải hăng hái mà bị bay màu ngay trên Live, đúng là khoảnh khắc dở khóc dở cười của anh em game thủ!</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #highlightgame #gamethu</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E746" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7601741440917441799</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Game khó mới biết ai là cao thủ, quả highlight này anh em chấm mấy điểm?</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #highlightgame #gamethu</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E747" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7576886340982164744</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Thất bại chỉ là bài học để tạo nên trận lội ngược dòng đỉnh cao thôi. Trận sau chắc chắn lấy lại Top 1 nhé anh em!</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #gamerviet</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E748" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7577630213249469704</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Pha xử lý bắn chay cân 6 cực gắt ngay trên livestream khiến cả phòng đấu ngỡ ngàng. Đẳng cấp tay to là đây chứ đâu!</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #highlightgame #gamethu</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E749" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kaito_live1/video/7578460574284107015</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Thua trận này thì ta bày trận khác, anh em sẵn sàng vào kéo Cường lại chưa?</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>#ucircle #cuongmegame #freefire #gameplay #gamerviet</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Cường Mê Game</t>
+        </is>
+      </c>
+      <c r="E750" t="n">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
